--- a/order book.xlsx
+++ b/order book.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7381" uniqueCount="3167">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7398" uniqueCount="3179">
   <si>
     <t>* 부가세(VAT) 포함 금액 기재 / 서브원 외에는 물품 "사진" 필수</t>
   </si>
@@ -9464,22 +9464,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>보관온도</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>RT</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>F</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>DF</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>1</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -9492,34 +9476,14 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>35w5</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>2w5w</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>RT</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>DF</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>22</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>afd</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
-    <t>RT</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>1</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -9528,10 +9492,6 @@
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
   <si>
-    <t>F</t>
-    <phoneticPr fontId="4" type="noConversion"/>
-  </si>
-  <si>
     <t>O</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
@@ -9565,6 +9525,94 @@
   </si>
   <si>
     <t>O</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>O</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Aldrich</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>100 mL</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>O</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>5g</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>O</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>aldrich</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>5g</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>o</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>25g</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>c0119</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>tci</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>o</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>tci</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>25g</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>b4263</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>o</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>tci</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>25g</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>B2065</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>o</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>o</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -37279,7 +37327,7 @@
   <sheetPr>
     <tabColor rgb="FFFFFF00"/>
   </sheetPr>
-  <dimension ref="A1:V1044939"/>
+  <dimension ref="A1:T1044939"/>
   <sheetFormatPr defaultColWidth="7.625" defaultRowHeight="16.5"/>
   <cols>
     <col min="1" max="1" width="7.125" style="5" customWidth="1"/>
@@ -37298,13 +37346,11 @@
     <col min="14" max="15" width="7.625" style="1"/>
     <col min="16" max="17" width="9" style="1" customWidth="1"/>
     <col min="18" max="18" width="9.625" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="10" style="1" customWidth="1"/>
-    <col min="20" max="20" width="7.625" style="1" customWidth="1"/>
-    <col min="21" max="21" width="7.625" style="1"/>
-    <col min="23" max="16384" width="7.625" style="1"/>
+    <col min="19" max="19" width="7.625" style="1" customWidth="1"/>
+    <col min="21" max="16384" width="7.625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" s="5" customFormat="1" ht="26.25" customHeight="1">
+    <row r="1" spans="1:19" s="5" customFormat="1" ht="26.25" customHeight="1">
       <c r="A1" s="233" t="s">
         <v>2145</v>
       </c>
@@ -37321,7 +37367,7 @@
       <c r="L1" s="234"/>
       <c r="M1" s="235"/>
     </row>
-    <row r="2" spans="1:21" s="5" customFormat="1" ht="19.5" customHeight="1">
+    <row r="2" spans="1:19" s="5" customFormat="1" ht="19.5" customHeight="1">
       <c r="A2" s="225" t="s">
         <v>2146</v>
       </c>
@@ -37338,7 +37384,7 @@
       <c r="L2" s="226"/>
       <c r="M2" s="227"/>
     </row>
-    <row r="3" spans="1:21" s="5" customFormat="1" ht="27" hidden="1" customHeight="1">
+    <row r="3" spans="1:19" s="5" customFormat="1" ht="27" hidden="1" customHeight="1">
       <c r="A3" s="238" t="s">
         <v>6</v>
       </c>
@@ -37355,7 +37401,7 @@
       <c r="L3" s="219"/>
       <c r="M3" s="219"/>
     </row>
-    <row r="4" spans="1:21" s="5" customFormat="1" ht="41.25" hidden="1" customHeight="1">
+    <row r="4" spans="1:19" s="5" customFormat="1" ht="41.25" hidden="1" customHeight="1">
       <c r="A4" s="228" t="s">
         <v>2147</v>
       </c>
@@ -37372,7 +37418,7 @@
       <c r="L4" s="219"/>
       <c r="M4" s="219"/>
     </row>
-    <row r="5" spans="1:21" s="5" customFormat="1" ht="21.75" customHeight="1">
+    <row r="5" spans="1:19" s="5" customFormat="1" ht="21.75" customHeight="1">
       <c r="A5" s="232" t="s">
         <v>2148</v>
       </c>
@@ -37389,7 +37435,7 @@
       <c r="L5" s="219"/>
       <c r="M5" s="219"/>
     </row>
-    <row r="6" spans="1:21" s="5" customFormat="1" ht="21.75" customHeight="1">
+    <row r="6" spans="1:19" s="5" customFormat="1" ht="21.75" customHeight="1">
       <c r="A6" s="218" t="s">
         <v>9</v>
       </c>
@@ -37406,7 +37452,7 @@
       <c r="L6" s="219"/>
       <c r="M6" s="220"/>
     </row>
-    <row r="7" spans="1:21" s="5" customFormat="1" ht="17.25" customHeight="1">
+    <row r="7" spans="1:19" s="5" customFormat="1" ht="17.25" customHeight="1">
       <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
@@ -37450,7 +37496,7 @@
         <v>26</v>
       </c>
       <c r="O7" s="5" t="s">
-        <v>3161</v>
+        <v>3151</v>
       </c>
       <c r="P7" s="5" t="s">
         <v>22</v>
@@ -37462,16 +37508,10 @@
         <v>23</v>
       </c>
       <c r="S7" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="T7" s="5" t="s">
         <v>25</v>
       </c>
-      <c r="U7" s="5" t="s">
-        <v>3141</v>
-      </c>
-    </row>
-    <row r="8" spans="1:21" s="175" customFormat="1" ht="15" customHeight="1">
+    </row>
+    <row r="8" spans="1:19" s="175" customFormat="1" ht="15" customHeight="1">
       <c r="A8" s="168" t="s">
         <v>2150</v>
       </c>
@@ -37498,7 +37538,7 @@
       <c r="L8" s="173"/>
       <c r="M8" s="174"/>
     </row>
-    <row r="9" spans="1:21" s="175" customFormat="1" ht="15" customHeight="1">
+    <row r="9" spans="1:19" s="175" customFormat="1" ht="15" customHeight="1">
       <c r="A9" s="168" t="s">
         <v>2153</v>
       </c>
@@ -37525,7 +37565,7 @@
       <c r="L9" s="173"/>
       <c r="M9" s="174"/>
     </row>
-    <row r="10" spans="1:21" s="175" customFormat="1" ht="15" customHeight="1">
+    <row r="10" spans="1:19" s="175" customFormat="1" ht="15" customHeight="1">
       <c r="A10" s="168" t="s">
         <v>2155</v>
       </c>
@@ -37552,7 +37592,7 @@
       <c r="L10" s="173"/>
       <c r="M10" s="174"/>
     </row>
-    <row r="11" spans="1:21" s="175" customFormat="1" ht="15" customHeight="1">
+    <row r="11" spans="1:19" s="175" customFormat="1" ht="15" customHeight="1">
       <c r="A11" s="168" t="s">
         <v>2158</v>
       </c>
@@ -37577,7 +37617,7 @@
       <c r="L11" s="173"/>
       <c r="M11" s="174"/>
     </row>
-    <row r="12" spans="1:21" s="175" customFormat="1" ht="15" customHeight="1">
+    <row r="12" spans="1:19" s="175" customFormat="1" ht="15" customHeight="1">
       <c r="A12" s="168" t="s">
         <v>2159</v>
       </c>
@@ -37604,7 +37644,7 @@
       <c r="L12" s="173"/>
       <c r="M12" s="174"/>
     </row>
-    <row r="13" spans="1:21" s="175" customFormat="1" ht="15" customHeight="1">
+    <row r="13" spans="1:19" s="175" customFormat="1" ht="15" customHeight="1">
       <c r="A13" s="168" t="s">
         <v>2161</v>
       </c>
@@ -37631,7 +37671,7 @@
       <c r="L13" s="173"/>
       <c r="M13" s="174"/>
     </row>
-    <row r="14" spans="1:21" s="175" customFormat="1" ht="15" customHeight="1">
+    <row r="14" spans="1:19" s="175" customFormat="1" ht="15" customHeight="1">
       <c r="A14" s="168" t="s">
         <v>2163</v>
       </c>
@@ -37657,7 +37697,7 @@
       <c r="L14" s="173"/>
       <c r="M14" s="174"/>
     </row>
-    <row r="15" spans="1:21" s="175" customFormat="1" ht="15" customHeight="1">
+    <row r="15" spans="1:19" s="175" customFormat="1" ht="15" customHeight="1">
       <c r="A15" s="168" t="s">
         <v>2165</v>
       </c>
@@ -37684,7 +37724,7 @@
       <c r="L15" s="173"/>
       <c r="M15" s="174"/>
     </row>
-    <row r="16" spans="1:21" s="175" customFormat="1" ht="15" customHeight="1">
+    <row r="16" spans="1:19" s="175" customFormat="1" ht="15" customHeight="1">
       <c r="A16" s="168" t="s">
         <v>2166</v>
       </c>
@@ -37712,17 +37752,14 @@
       </c>
       <c r="L16" s="173"/>
       <c r="M16" s="174"/>
-      <c r="N16" s="217" t="s">
+      <c r="N16" s="175" t="s">
         <v>2015</v>
       </c>
       <c r="O16" s="217" t="s">
         <v>2015</v>
       </c>
-      <c r="U16" s="175" t="s">
-        <v>3142</v>
-      </c>
-    </row>
-    <row r="17" spans="1:21" s="175" customFormat="1" ht="15" customHeight="1">
+    </row>
+    <row r="17" spans="1:19" s="175" customFormat="1" ht="15" customHeight="1">
       <c r="A17" s="168" t="s">
         <v>2168</v>
       </c>
@@ -37749,7 +37786,7 @@
       <c r="L17" s="173"/>
       <c r="M17" s="174"/>
     </row>
-    <row r="18" spans="1:21" s="175" customFormat="1" ht="15" customHeight="1">
+    <row r="18" spans="1:19" s="175" customFormat="1" ht="15" customHeight="1">
       <c r="A18" s="168" t="s">
         <v>2170</v>
       </c>
@@ -37774,7 +37811,7 @@
       <c r="L18" s="173"/>
       <c r="M18" s="174"/>
     </row>
-    <row r="19" spans="1:21" s="175" customFormat="1" ht="15" customHeight="1">
+    <row r="19" spans="1:19" s="175" customFormat="1" ht="15" customHeight="1">
       <c r="A19" s="168" t="s">
         <v>2171</v>
       </c>
@@ -37799,7 +37836,7 @@
       <c r="L19" s="173"/>
       <c r="M19" s="174"/>
     </row>
-    <row r="20" spans="1:21" s="175" customFormat="1" ht="15" customHeight="1">
+    <row r="20" spans="1:19" s="175" customFormat="1" ht="15" customHeight="1">
       <c r="A20" s="168" t="s">
         <v>2172</v>
       </c>
@@ -37828,7 +37865,7 @@
       <c r="L20" s="173"/>
       <c r="M20" s="174"/>
     </row>
-    <row r="21" spans="1:21" s="175" customFormat="1" ht="15" customHeight="1">
+    <row r="21" spans="1:19" s="175" customFormat="1" ht="15" customHeight="1">
       <c r="A21" s="168" t="s">
         <v>2173</v>
       </c>
@@ -37858,7 +37895,7 @@
       </c>
       <c r="L21" s="173"/>
       <c r="M21" s="174"/>
-      <c r="N21" s="217" t="s">
+      <c r="N21" s="175" t="s">
         <v>2015</v>
       </c>
       <c r="O21" s="217" t="s">
@@ -37874,16 +37911,10 @@
         <v>2174</v>
       </c>
       <c r="S21" s="175" t="s">
-        <v>2013</v>
-      </c>
-      <c r="T21" s="175" t="s">
         <v>2014</v>
       </c>
-      <c r="U21" s="175" t="s">
-        <v>3142</v>
-      </c>
-    </row>
-    <row r="22" spans="1:21" s="175" customFormat="1" ht="15" customHeight="1">
+    </row>
+    <row r="22" spans="1:19" s="175" customFormat="1" ht="15" customHeight="1">
       <c r="A22" s="168" t="s">
         <v>2175</v>
       </c>
@@ -37911,7 +37942,7 @@
       </c>
       <c r="L22" s="173"/>
       <c r="M22" s="174"/>
-      <c r="N22" s="217" t="s">
+      <c r="N22" s="175" t="s">
         <v>2015</v>
       </c>
       <c r="O22" s="217" t="s">
@@ -37927,16 +37958,10 @@
         <v>2177</v>
       </c>
       <c r="S22" s="175" t="s">
-        <v>2013</v>
-      </c>
-      <c r="T22" s="175" t="s">
         <v>2014</v>
       </c>
-      <c r="U22" s="175" t="s">
-        <v>3143</v>
-      </c>
-    </row>
-    <row r="23" spans="1:21" s="175" customFormat="1" ht="15" customHeight="1">
+    </row>
+    <row r="23" spans="1:19" s="175" customFormat="1" ht="15" customHeight="1">
       <c r="A23" s="168" t="s">
         <v>2178</v>
       </c>
@@ -37963,7 +37988,7 @@
       <c r="L23" s="173"/>
       <c r="M23" s="174"/>
     </row>
-    <row r="24" spans="1:21" s="175" customFormat="1" ht="15" customHeight="1">
+    <row r="24" spans="1:19" s="175" customFormat="1" ht="15" customHeight="1">
       <c r="A24" s="168" t="s">
         <v>2181</v>
       </c>
@@ -37989,7 +38014,7 @@
       <c r="L24" s="173"/>
       <c r="M24" s="174"/>
     </row>
-    <row r="25" spans="1:21" s="175" customFormat="1" ht="15" customHeight="1">
+    <row r="25" spans="1:19" s="175" customFormat="1" ht="15" customHeight="1">
       <c r="A25" s="168" t="s">
         <v>2183</v>
       </c>
@@ -38014,7 +38039,7 @@
       <c r="L25" s="173"/>
       <c r="M25" s="174"/>
     </row>
-    <row r="26" spans="1:21" s="175" customFormat="1" ht="15" customHeight="1">
+    <row r="26" spans="1:19" s="175" customFormat="1" ht="15" customHeight="1">
       <c r="A26" s="168" t="s">
         <v>2186</v>
       </c>
@@ -38039,7 +38064,7 @@
       <c r="L26" s="173"/>
       <c r="M26" s="174"/>
     </row>
-    <row r="27" spans="1:21" s="175" customFormat="1" ht="15" customHeight="1">
+    <row r="27" spans="1:19" s="175" customFormat="1" ht="15" customHeight="1">
       <c r="A27" s="168" t="s">
         <v>2188</v>
       </c>
@@ -38064,7 +38089,7 @@
       <c r="L27" s="173"/>
       <c r="M27" s="174"/>
     </row>
-    <row r="28" spans="1:21" s="175" customFormat="1" ht="15" customHeight="1">
+    <row r="28" spans="1:19" s="175" customFormat="1" ht="15" customHeight="1">
       <c r="A28" s="168" t="s">
         <v>2189</v>
       </c>
@@ -38089,7 +38114,7 @@
       <c r="L28" s="173"/>
       <c r="M28" s="174"/>
     </row>
-    <row r="29" spans="1:21" s="175" customFormat="1" ht="15" customHeight="1">
+    <row r="29" spans="1:19" s="175" customFormat="1" ht="15" customHeight="1">
       <c r="A29" s="168" t="s">
         <v>2191</v>
       </c>
@@ -38116,7 +38141,7 @@
       <c r="L29" s="173"/>
       <c r="M29" s="174"/>
     </row>
-    <row r="30" spans="1:21" s="175" customFormat="1" ht="15" customHeight="1">
+    <row r="30" spans="1:19" s="175" customFormat="1" ht="15" customHeight="1">
       <c r="A30" s="168" t="s">
         <v>2192</v>
       </c>
@@ -38143,7 +38168,7 @@
       <c r="L30" s="173"/>
       <c r="M30" s="174"/>
     </row>
-    <row r="31" spans="1:21" s="175" customFormat="1" ht="15" customHeight="1">
+    <row r="31" spans="1:19" s="175" customFormat="1" ht="15" customHeight="1">
       <c r="A31" s="168" t="s">
         <v>2193</v>
       </c>
@@ -38170,7 +38195,7 @@
       <c r="L31" s="173"/>
       <c r="M31" s="174"/>
     </row>
-    <row r="32" spans="1:21" s="175" customFormat="1" ht="15" customHeight="1">
+    <row r="32" spans="1:19" s="175" customFormat="1" ht="15" customHeight="1">
       <c r="A32" s="168" t="s">
         <v>2195</v>
       </c>
@@ -38198,7 +38223,7 @@
       </c>
       <c r="L32" s="173"/>
       <c r="M32" s="174"/>
-      <c r="N32" s="217" t="s">
+      <c r="N32" s="175" t="s">
         <v>2015</v>
       </c>
       <c r="O32" s="217" t="s">
@@ -38214,16 +38239,10 @@
         <v>2177</v>
       </c>
       <c r="S32" s="175" t="s">
-        <v>2013</v>
-      </c>
-      <c r="T32" s="175" t="s">
         <v>2014</v>
       </c>
-      <c r="U32" s="175" t="s">
-        <v>3144</v>
-      </c>
-    </row>
-    <row r="33" spans="1:21" s="175" customFormat="1" ht="15" customHeight="1">
+    </row>
+    <row r="33" spans="1:19" s="175" customFormat="1" ht="15" customHeight="1">
       <c r="A33" s="168" t="s">
         <v>2197</v>
       </c>
@@ -38250,7 +38269,7 @@
       <c r="L33" s="173"/>
       <c r="M33" s="174"/>
     </row>
-    <row r="34" spans="1:21" s="175" customFormat="1" ht="15" customHeight="1">
+    <row r="34" spans="1:19" s="175" customFormat="1" ht="15" customHeight="1">
       <c r="A34" s="168" t="s">
         <v>2199</v>
       </c>
@@ -38275,7 +38294,7 @@
       <c r="L34" s="173"/>
       <c r="M34" s="174"/>
     </row>
-    <row r="35" spans="1:21" s="175" customFormat="1" ht="15" customHeight="1">
+    <row r="35" spans="1:19" s="175" customFormat="1" ht="15" customHeight="1">
       <c r="A35" s="168" t="s">
         <v>2200</v>
       </c>
@@ -38302,7 +38321,7 @@
       <c r="L35" s="173"/>
       <c r="M35" s="174"/>
     </row>
-    <row r="36" spans="1:21" s="175" customFormat="1" ht="15" customHeight="1">
+    <row r="36" spans="1:19" s="175" customFormat="1" ht="15" customHeight="1">
       <c r="A36" s="168" t="s">
         <v>2202</v>
       </c>
@@ -38329,7 +38348,7 @@
       <c r="L36" s="173"/>
       <c r="M36" s="174"/>
     </row>
-    <row r="37" spans="1:21" s="175" customFormat="1" ht="15" customHeight="1">
+    <row r="37" spans="1:19" s="175" customFormat="1" ht="15" customHeight="1">
       <c r="A37" s="168" t="s">
         <v>2204</v>
       </c>
@@ -38356,7 +38375,7 @@
       <c r="L37" s="173"/>
       <c r="M37" s="174"/>
     </row>
-    <row r="38" spans="1:21" s="175" customFormat="1" ht="15" customHeight="1">
+    <row r="38" spans="1:19" s="175" customFormat="1" ht="15" customHeight="1">
       <c r="A38" s="168" t="s">
         <v>2206</v>
       </c>
@@ -38383,7 +38402,7 @@
       <c r="L38" s="173"/>
       <c r="M38" s="174"/>
     </row>
-    <row r="39" spans="1:21" s="175" customFormat="1" ht="15" customHeight="1">
+    <row r="39" spans="1:19" s="175" customFormat="1" ht="15" customHeight="1">
       <c r="A39" s="168" t="s">
         <v>2208</v>
       </c>
@@ -38410,7 +38429,7 @@
       <c r="L39" s="173"/>
       <c r="M39" s="174"/>
     </row>
-    <row r="40" spans="1:21" s="175" customFormat="1" ht="15" customHeight="1">
+    <row r="40" spans="1:19" s="175" customFormat="1" ht="15" customHeight="1">
       <c r="A40" s="168" t="s">
         <v>2210</v>
       </c>
@@ -38438,14 +38457,14 @@
       </c>
       <c r="L40" s="173"/>
       <c r="M40" s="174"/>
-      <c r="N40" s="217" t="s">
+      <c r="N40" s="175" t="s">
         <v>2015</v>
       </c>
       <c r="O40" s="217" t="s">
         <v>2015</v>
       </c>
     </row>
-    <row r="41" spans="1:21" s="175" customFormat="1" ht="15" customHeight="1">
+    <row r="41" spans="1:19" s="175" customFormat="1" ht="15" customHeight="1">
       <c r="A41" s="168" t="s">
         <v>2211</v>
       </c>
@@ -38472,7 +38491,7 @@
       <c r="L41" s="173"/>
       <c r="M41" s="174"/>
     </row>
-    <row r="42" spans="1:21" s="175" customFormat="1" ht="15" customHeight="1">
+    <row r="42" spans="1:19" s="175" customFormat="1" ht="15" customHeight="1">
       <c r="A42" s="168" t="s">
         <v>2214</v>
       </c>
@@ -38499,7 +38518,7 @@
       <c r="L42" s="173"/>
       <c r="M42" s="174"/>
     </row>
-    <row r="43" spans="1:21" s="175" customFormat="1" ht="15" customHeight="1">
+    <row r="43" spans="1:19" s="175" customFormat="1" ht="15" customHeight="1">
       <c r="A43" s="168" t="s">
         <v>2215</v>
       </c>
@@ -38524,7 +38543,7 @@
       <c r="L43" s="173"/>
       <c r="M43" s="174"/>
     </row>
-    <row r="44" spans="1:21" s="175" customFormat="1" ht="15" customHeight="1">
+    <row r="44" spans="1:19" s="175" customFormat="1" ht="15" customHeight="1">
       <c r="A44" s="168" t="s">
         <v>2218</v>
       </c>
@@ -38551,7 +38570,7 @@
       <c r="L44" s="173"/>
       <c r="M44" s="174"/>
     </row>
-    <row r="45" spans="1:21" s="175" customFormat="1" ht="15" customHeight="1">
+    <row r="45" spans="1:19" s="175" customFormat="1" ht="15" customHeight="1">
       <c r="A45" s="168" t="s">
         <v>2220</v>
       </c>
@@ -38575,36 +38594,30 @@
         <v>349800</v>
       </c>
       <c r="K45" s="172" t="s">
-        <v>3145</v>
+        <v>3141</v>
       </c>
       <c r="L45" s="173"/>
       <c r="M45" s="174"/>
-      <c r="N45" s="217" t="s">
+      <c r="N45" s="175" t="s">
         <v>2015</v>
       </c>
       <c r="O45" s="217" t="s">
         <v>2015</v>
       </c>
       <c r="P45" s="175" t="s">
-        <v>3146</v>
+        <v>3142</v>
       </c>
       <c r="Q45" s="175">
         <v>2</v>
       </c>
       <c r="R45" s="175" t="s">
-        <v>3147</v>
+        <v>3143</v>
       </c>
       <c r="S45" s="175" t="s">
-        <v>3148</v>
-      </c>
-      <c r="T45" s="175" t="s">
-        <v>3149</v>
-      </c>
-      <c r="U45" s="175" t="s">
-        <v>3150</v>
-      </c>
-    </row>
-    <row r="46" spans="1:21" s="175" customFormat="1" ht="15" customHeight="1">
+        <v>3144</v>
+      </c>
+    </row>
+    <row r="46" spans="1:19" s="175" customFormat="1" ht="15" customHeight="1">
       <c r="A46" s="168" t="s">
         <v>2222</v>
       </c>
@@ -38629,7 +38642,7 @@
       <c r="L46" s="173"/>
       <c r="M46" s="174"/>
     </row>
-    <row r="47" spans="1:21" s="175" customFormat="1" ht="15" customHeight="1">
+    <row r="47" spans="1:19" s="175" customFormat="1" ht="15" customHeight="1">
       <c r="A47" s="168" t="s">
         <v>2224</v>
       </c>
@@ -38653,36 +38666,30 @@
         <v>438900</v>
       </c>
       <c r="K47" s="172" t="s">
-        <v>3152</v>
+        <v>3145</v>
       </c>
       <c r="L47" s="173"/>
       <c r="M47" s="174"/>
-      <c r="N47" s="217" t="s">
+      <c r="N47" s="175" t="s">
         <v>2015</v>
       </c>
       <c r="O47" s="217" t="s">
         <v>2015</v>
       </c>
       <c r="P47" s="175" t="s">
-        <v>3146</v>
+        <v>3142</v>
       </c>
       <c r="Q47" s="175">
         <v>2</v>
       </c>
       <c r="R47" s="175" t="s">
-        <v>3147</v>
+        <v>3143</v>
       </c>
       <c r="S47" s="175" t="s">
-        <v>3148</v>
-      </c>
-      <c r="T47" s="175" t="s">
-        <v>3149</v>
-      </c>
-      <c r="U47" s="175" t="s">
-        <v>3151</v>
-      </c>
-    </row>
-    <row r="48" spans="1:21" s="175" customFormat="1" ht="15" customHeight="1">
+        <v>3144</v>
+      </c>
+    </row>
+    <row r="48" spans="1:19" s="175" customFormat="1" ht="15" customHeight="1">
       <c r="A48" s="168" t="s">
         <v>2226</v>
       </c>
@@ -38709,7 +38716,7 @@
       <c r="L48" s="173"/>
       <c r="M48" s="174"/>
     </row>
-    <row r="49" spans="1:21" s="175" customFormat="1" ht="15" customHeight="1">
+    <row r="49" spans="1:19" s="175" customFormat="1" ht="15" customHeight="1">
       <c r="A49" s="168" t="s">
         <v>2229</v>
       </c>
@@ -38736,7 +38743,7 @@
       <c r="L49" s="173"/>
       <c r="M49" s="174"/>
     </row>
-    <row r="50" spans="1:21" s="175" customFormat="1" ht="15" customHeight="1">
+    <row r="50" spans="1:19" s="175" customFormat="1" ht="15" customHeight="1">
       <c r="A50" s="168" t="s">
         <v>2231</v>
       </c>
@@ -38764,14 +38771,14 @@
       </c>
       <c r="L50" s="173"/>
       <c r="M50" s="174"/>
-      <c r="N50" s="217" t="s">
+      <c r="N50" s="175" t="s">
         <v>2015</v>
       </c>
       <c r="O50" s="217" t="s">
         <v>2015</v>
       </c>
     </row>
-    <row r="51" spans="1:21" s="175" customFormat="1" ht="15" customHeight="1">
+    <row r="51" spans="1:19" s="175" customFormat="1" ht="15" customHeight="1">
       <c r="A51" s="168" t="s">
         <v>2234</v>
       </c>
@@ -38800,7 +38807,7 @@
       <c r="L51" s="173"/>
       <c r="M51" s="174"/>
     </row>
-    <row r="52" spans="1:21" s="175" customFormat="1" ht="15" customHeight="1">
+    <row r="52" spans="1:19" s="175" customFormat="1" ht="15" customHeight="1">
       <c r="A52" s="168" t="s">
         <v>2236</v>
       </c>
@@ -38828,14 +38835,14 @@
       </c>
       <c r="L52" s="173"/>
       <c r="M52" s="174"/>
-      <c r="N52" s="217" t="s">
+      <c r="N52" s="175" t="s">
         <v>2015</v>
       </c>
       <c r="O52" s="217" t="s">
         <v>2015</v>
       </c>
     </row>
-    <row r="53" spans="1:21" s="175" customFormat="1" ht="15" customHeight="1">
+    <row r="53" spans="1:19" s="175" customFormat="1" ht="15" customHeight="1">
       <c r="A53" s="168" t="s">
         <v>2238</v>
       </c>
@@ -38862,7 +38869,7 @@
       <c r="L53" s="173"/>
       <c r="M53" s="174"/>
     </row>
-    <row r="54" spans="1:21" s="175" customFormat="1" ht="17.25" customHeight="1">
+    <row r="54" spans="1:19" s="175" customFormat="1" ht="17.25" customHeight="1">
       <c r="A54" s="168" t="s">
         <v>2240</v>
       </c>
@@ -38887,7 +38894,7 @@
       <c r="L54" s="173"/>
       <c r="M54" s="174"/>
     </row>
-    <row r="55" spans="1:21" s="175" customFormat="1" ht="17.25" customHeight="1">
+    <row r="55" spans="1:19" s="175" customFormat="1" ht="17.25" customHeight="1">
       <c r="A55" s="168" t="s">
         <v>2242</v>
       </c>
@@ -38912,7 +38919,7 @@
       <c r="L55" s="173"/>
       <c r="M55" s="174"/>
     </row>
-    <row r="56" spans="1:21" s="175" customFormat="1" ht="17.25" customHeight="1">
+    <row r="56" spans="1:19" s="175" customFormat="1" ht="17.25" customHeight="1">
       <c r="A56" s="168" t="s">
         <v>2244</v>
       </c>
@@ -38940,14 +38947,14 @@
       </c>
       <c r="L56" s="173"/>
       <c r="M56" s="174"/>
-      <c r="N56" s="217" t="s">
+      <c r="N56" s="175" t="s">
         <v>2015</v>
       </c>
       <c r="O56" s="217" t="s">
         <v>2015</v>
       </c>
     </row>
-    <row r="57" spans="1:21" s="175" customFormat="1" ht="17.25" customHeight="1">
+    <row r="57" spans="1:19" s="175" customFormat="1" ht="17.25" customHeight="1">
       <c r="A57" s="180" t="s">
         <v>2246</v>
       </c>
@@ -38974,7 +38981,7 @@
       <c r="L57" s="190"/>
       <c r="M57" s="191"/>
     </row>
-    <row r="58" spans="1:21" s="175" customFormat="1" ht="17.25" customHeight="1">
+    <row r="58" spans="1:19" s="175" customFormat="1" ht="17.25" customHeight="1">
       <c r="A58" s="168" t="s">
         <v>2247</v>
       </c>
@@ -39001,7 +39008,7 @@
       <c r="L58" s="172"/>
       <c r="M58" s="174"/>
     </row>
-    <row r="59" spans="1:21" s="175" customFormat="1" ht="17.25" customHeight="1">
+    <row r="59" spans="1:19" s="175" customFormat="1" ht="17.25" customHeight="1">
       <c r="A59" s="168" t="s">
         <v>2250</v>
       </c>
@@ -39028,7 +39035,7 @@
       <c r="L59" s="172"/>
       <c r="M59" s="174"/>
     </row>
-    <row r="60" spans="1:21" s="175" customFormat="1" ht="17.25" customHeight="1">
+    <row r="60" spans="1:19" s="175" customFormat="1" ht="17.25" customHeight="1">
       <c r="A60" s="168" t="s">
         <v>2252</v>
       </c>
@@ -39053,7 +39060,7 @@
       <c r="L60" s="172"/>
       <c r="M60" s="174"/>
     </row>
-    <row r="61" spans="1:21" s="175" customFormat="1" ht="17.25" customHeight="1">
+    <row r="61" spans="1:19" s="175" customFormat="1" ht="17.25" customHeight="1">
       <c r="A61" s="168" t="s">
         <v>2253</v>
       </c>
@@ -39080,7 +39087,7 @@
       <c r="L61" s="169"/>
       <c r="M61" s="168"/>
     </row>
-    <row r="62" spans="1:21" s="175" customFormat="1" ht="17.25" customHeight="1">
+    <row r="62" spans="1:19" s="175" customFormat="1" ht="17.25" customHeight="1">
       <c r="A62" s="168" t="s">
         <v>2255</v>
       </c>
@@ -39107,7 +39114,7 @@
       <c r="L62" s="169"/>
       <c r="M62" s="168"/>
     </row>
-    <row r="63" spans="1:21" s="175" customFormat="1" ht="17.25" customHeight="1">
+    <row r="63" spans="1:19" s="175" customFormat="1" ht="17.25" customHeight="1">
       <c r="A63" s="168" t="s">
         <v>2258</v>
       </c>
@@ -39134,7 +39141,7 @@
       <c r="L63" s="169"/>
       <c r="M63" s="168"/>
     </row>
-    <row r="64" spans="1:21" s="175" customFormat="1" ht="17.25" customHeight="1">
+    <row r="64" spans="1:19" s="175" customFormat="1" ht="17.25" customHeight="1">
       <c r="A64" s="194" t="s">
         <v>2259</v>
       </c>
@@ -39162,7 +39169,7 @@
       </c>
       <c r="L64" s="169"/>
       <c r="M64" s="168"/>
-      <c r="N64" s="217" t="s">
+      <c r="N64" s="175" t="s">
         <v>2015</v>
       </c>
       <c r="O64" s="217" t="s">
@@ -39177,14 +39184,8 @@
       <c r="R64" s="175">
         <v>1</v>
       </c>
-      <c r="S64" s="175" t="s">
-        <v>3153</v>
-      </c>
-      <c r="T64" s="175">
+      <c r="S64" s="175">
         <v>1</v>
-      </c>
-      <c r="U64" s="175" t="s">
-        <v>3154</v>
       </c>
     </row>
     <row r="65" spans="1:15" s="175" customFormat="1" ht="17.25" customHeight="1">
@@ -39269,7 +39270,7 @@
       </c>
       <c r="L67" s="169"/>
       <c r="M67" s="168"/>
-      <c r="N67" s="217" t="s">
+      <c r="N67" s="175" t="s">
         <v>2015</v>
       </c>
       <c r="O67" s="217" t="s">
@@ -39627,7 +39628,7 @@
       <c r="L80" s="169"/>
       <c r="M80" s="168"/>
     </row>
-    <row r="81" spans="1:21" s="175" customFormat="1" ht="17.25" customHeight="1">
+    <row r="81" spans="1:18" s="175" customFormat="1" ht="17.25" customHeight="1">
       <c r="A81" s="168" t="s">
         <v>2296</v>
       </c>
@@ -39654,7 +39655,7 @@
       <c r="L81" s="169"/>
       <c r="M81" s="168"/>
     </row>
-    <row r="82" spans="1:21" s="175" customFormat="1" ht="17.25" customHeight="1">
+    <row r="82" spans="1:18" s="175" customFormat="1" ht="17.25" customHeight="1">
       <c r="A82" s="168" t="s">
         <v>2298</v>
       </c>
@@ -39681,7 +39682,7 @@
       <c r="L82" s="169"/>
       <c r="M82" s="168"/>
     </row>
-    <row r="83" spans="1:21" s="175" customFormat="1" ht="17.25" customHeight="1">
+    <row r="83" spans="1:18" s="175" customFormat="1" ht="17.25" customHeight="1">
       <c r="A83" s="168" t="s">
         <v>2299</v>
       </c>
@@ -39708,7 +39709,7 @@
       <c r="L83" s="169"/>
       <c r="M83" s="168"/>
     </row>
-    <row r="84" spans="1:21" s="175" customFormat="1" ht="17.25" customHeight="1">
+    <row r="84" spans="1:18" s="175" customFormat="1" ht="17.25" customHeight="1">
       <c r="A84" s="168" t="s">
         <v>2301</v>
       </c>
@@ -39735,7 +39736,7 @@
       <c r="L84" s="169"/>
       <c r="M84" s="168"/>
     </row>
-    <row r="85" spans="1:21" s="175" customFormat="1" ht="17.25" customHeight="1">
+    <row r="85" spans="1:18" s="175" customFormat="1" ht="17.25" customHeight="1">
       <c r="A85" s="168" t="s">
         <v>2304</v>
       </c>
@@ -39759,27 +39760,24 @@
         <v>566500</v>
       </c>
       <c r="K85" s="169" t="s">
-        <v>3155</v>
+        <v>3146</v>
       </c>
       <c r="L85" s="169"/>
       <c r="M85" s="168"/>
-      <c r="N85" s="217" t="s">
+      <c r="N85" s="175" t="s">
         <v>2015</v>
       </c>
       <c r="O85" s="217" t="s">
-        <v>3162</v>
+        <v>3152</v>
       </c>
       <c r="Q85" s="175">
         <v>1</v>
       </c>
       <c r="R85" s="175" t="s">
-        <v>3156</v>
-      </c>
-      <c r="U85" s="175" t="s">
-        <v>3157</v>
-      </c>
-    </row>
-    <row r="86" spans="1:21" s="175" customFormat="1" ht="17.25" customHeight="1">
+        <v>3147</v>
+      </c>
+    </row>
+    <row r="86" spans="1:18" s="175" customFormat="1" ht="17.25" customHeight="1">
       <c r="A86" s="168" t="s">
         <v>2306</v>
       </c>
@@ -39806,7 +39804,7 @@
       <c r="L86" s="169"/>
       <c r="M86" s="168"/>
     </row>
-    <row r="87" spans="1:21" s="175" customFormat="1" ht="17.25" customHeight="1">
+    <row r="87" spans="1:18" s="175" customFormat="1" ht="17.25" customHeight="1">
       <c r="A87" s="168" t="s">
         <v>2307</v>
       </c>
@@ -39833,7 +39831,7 @@
       <c r="L87" s="169"/>
       <c r="M87" s="168"/>
     </row>
-    <row r="88" spans="1:21" s="175" customFormat="1" ht="17.25" customHeight="1">
+    <row r="88" spans="1:18" s="175" customFormat="1" ht="17.25" customHeight="1">
       <c r="A88" s="168" t="s">
         <v>2309</v>
       </c>
@@ -39860,7 +39858,7 @@
       <c r="L88" s="169"/>
       <c r="M88" s="168"/>
     </row>
-    <row r="89" spans="1:21" s="175" customFormat="1" ht="17.25" customHeight="1">
+    <row r="89" spans="1:18" s="175" customFormat="1" ht="17.25" customHeight="1">
       <c r="A89" s="168" t="s">
         <v>2311</v>
       </c>
@@ -39885,7 +39883,7 @@
       <c r="L89" s="169"/>
       <c r="M89" s="168"/>
     </row>
-    <row r="90" spans="1:21" s="175" customFormat="1" ht="17.25" customHeight="1">
+    <row r="90" spans="1:18" s="175" customFormat="1" ht="17.25" customHeight="1">
       <c r="A90" s="168" t="s">
         <v>2314</v>
       </c>
@@ -39912,7 +39910,7 @@
       <c r="L90" s="169"/>
       <c r="M90" s="168"/>
     </row>
-    <row r="91" spans="1:21" s="175" customFormat="1" ht="17.25" customHeight="1">
+    <row r="91" spans="1:18" s="175" customFormat="1" ht="17.25" customHeight="1">
       <c r="A91" s="168" t="s">
         <v>2317</v>
       </c>
@@ -39939,7 +39937,7 @@
       <c r="L91" s="169"/>
       <c r="M91" s="168"/>
     </row>
-    <row r="92" spans="1:21" s="175" customFormat="1" ht="17.25" customHeight="1">
+    <row r="92" spans="1:18" s="175" customFormat="1" ht="17.25" customHeight="1">
       <c r="A92" s="168" t="s">
         <v>2319</v>
       </c>
@@ -39966,7 +39964,7 @@
       <c r="L92" s="169"/>
       <c r="M92" s="168"/>
     </row>
-    <row r="93" spans="1:21" s="175" customFormat="1" ht="17.25" customHeight="1">
+    <row r="93" spans="1:18" s="175" customFormat="1" ht="17.25" customHeight="1">
       <c r="A93" s="168" t="s">
         <v>2320</v>
       </c>
@@ -39993,7 +39991,7 @@
       <c r="L93" s="169"/>
       <c r="M93" s="168"/>
     </row>
-    <row r="94" spans="1:21" s="175" customFormat="1" ht="17.25" customHeight="1">
+    <row r="94" spans="1:18" s="175" customFormat="1" ht="17.25" customHeight="1">
       <c r="A94" s="168" t="s">
         <v>2323</v>
       </c>
@@ -40020,7 +40018,7 @@
       <c r="L94" s="169"/>
       <c r="M94" s="168"/>
     </row>
-    <row r="95" spans="1:21" s="175" customFormat="1" ht="17.25" customHeight="1">
+    <row r="95" spans="1:18" s="175" customFormat="1" ht="17.25" customHeight="1">
       <c r="A95" s="168" t="s">
         <v>2325</v>
       </c>
@@ -40049,7 +40047,7 @@
       <c r="L95" s="169"/>
       <c r="M95" s="168"/>
     </row>
-    <row r="96" spans="1:21" s="175" customFormat="1" ht="17.25" customHeight="1">
+    <row r="96" spans="1:18" s="175" customFormat="1" ht="17.25" customHeight="1">
       <c r="A96" s="168" t="s">
         <v>2327</v>
       </c>
@@ -40424,12 +40422,12 @@
         <v>364100</v>
       </c>
       <c r="K109" s="169" t="s">
-        <v>3155</v>
+        <v>3146</v>
       </c>
       <c r="L109" s="169"/>
       <c r="M109" s="168"/>
-      <c r="N109" s="217" t="s">
-        <v>3158</v>
+      <c r="N109" s="175" t="s">
+        <v>3148</v>
       </c>
       <c r="O109" s="217" t="s">
         <v>3139</v>
@@ -40758,7 +40756,7 @@
       </c>
       <c r="L121" s="169"/>
       <c r="M121" s="168"/>
-      <c r="N121" s="217" t="s">
+      <c r="N121" s="175" t="s">
         <v>3139</v>
       </c>
       <c r="O121" s="217" t="s">
@@ -41061,12 +41059,12 @@
         <v>467500</v>
       </c>
       <c r="K132" s="169" t="s">
-        <v>3159</v>
+        <v>3149</v>
       </c>
       <c r="L132" s="169"/>
       <c r="M132" s="168"/>
-      <c r="N132" s="217" t="s">
-        <v>3160</v>
+      <c r="N132" s="175" t="s">
+        <v>3150</v>
       </c>
       <c r="O132" s="217" t="s">
         <v>3139</v>
@@ -41351,7 +41349,7 @@
       </c>
       <c r="L142" s="169"/>
       <c r="M142" s="168"/>
-      <c r="N142" s="217" t="s">
+      <c r="N142" s="175" t="s">
         <v>3139</v>
       </c>
       <c r="O142" s="217" t="s">
@@ -41440,7 +41438,7 @@
       </c>
       <c r="L145" s="169"/>
       <c r="M145" s="168"/>
-      <c r="N145" s="217" t="s">
+      <c r="N145" s="175" t="s">
         <v>3139</v>
       </c>
       <c r="O145" s="217" t="s">
@@ -44511,7 +44509,7 @@
       <c r="L256" s="169"/>
       <c r="M256" s="168"/>
     </row>
-    <row r="257" spans="1:20" s="175" customFormat="1" ht="16.5" customHeight="1">
+    <row r="257" spans="1:19" s="175" customFormat="1" ht="16.5" customHeight="1">
       <c r="A257" s="194" t="s">
         <v>2642</v>
       </c>
@@ -44538,7 +44536,7 @@
       <c r="L257" s="169"/>
       <c r="M257" s="168"/>
     </row>
-    <row r="258" spans="1:20" s="175" customFormat="1" ht="16.5" customHeight="1">
+    <row r="258" spans="1:19" s="175" customFormat="1" ht="16.5" customHeight="1">
       <c r="A258" s="194" t="s">
         <v>2644</v>
       </c>
@@ -44565,11 +44563,11 @@
       <c r="N258" s="175" t="s">
         <v>1083</v>
       </c>
-      <c r="T258" s="175" t="s">
+      <c r="S258" s="175" t="s">
         <v>1083</v>
       </c>
     </row>
-    <row r="259" spans="1:20" s="175" customFormat="1" ht="16.5" customHeight="1">
+    <row r="259" spans="1:19" s="175" customFormat="1" ht="16.5" customHeight="1">
       <c r="A259" s="194" t="s">
         <v>2646</v>
       </c>
@@ -44594,7 +44592,7 @@
       <c r="L259" s="169"/>
       <c r="M259" s="168"/>
     </row>
-    <row r="260" spans="1:20" s="175" customFormat="1" ht="16.5" customHeight="1">
+    <row r="260" spans="1:19" s="175" customFormat="1" ht="16.5" customHeight="1">
       <c r="A260" s="194" t="s">
         <v>2648</v>
       </c>
@@ -44623,7 +44621,7 @@
       <c r="L260" s="169"/>
       <c r="M260" s="168"/>
     </row>
-    <row r="261" spans="1:20" s="175" customFormat="1" ht="16.5" customHeight="1">
+    <row r="261" spans="1:19" s="175" customFormat="1" ht="16.5" customHeight="1">
       <c r="A261" s="194" t="s">
         <v>2651</v>
       </c>
@@ -44652,7 +44650,7 @@
       <c r="L261" s="169"/>
       <c r="M261" s="168"/>
     </row>
-    <row r="262" spans="1:20" s="175" customFormat="1" ht="16.5" customHeight="1">
+    <row r="262" spans="1:19" s="175" customFormat="1" ht="16.5" customHeight="1">
       <c r="A262" s="194" t="s">
         <v>2653</v>
       </c>
@@ -44679,7 +44677,7 @@
       <c r="L262" s="169"/>
       <c r="M262" s="168"/>
     </row>
-    <row r="263" spans="1:20" s="175" customFormat="1" ht="16.5" customHeight="1">
+    <row r="263" spans="1:19" s="175" customFormat="1" ht="16.5" customHeight="1">
       <c r="A263" s="194" t="s">
         <v>2654</v>
       </c>
@@ -44706,7 +44704,7 @@
       <c r="L263" s="169"/>
       <c r="M263" s="168"/>
     </row>
-    <row r="264" spans="1:20" s="175" customFormat="1" ht="16.5" customHeight="1">
+    <row r="264" spans="1:19" s="175" customFormat="1" ht="16.5" customHeight="1">
       <c r="A264" s="194" t="s">
         <v>2656</v>
       </c>
@@ -44733,7 +44731,7 @@
       <c r="L264" s="169"/>
       <c r="M264" s="168"/>
     </row>
-    <row r="265" spans="1:20" s="175" customFormat="1" ht="16.5" customHeight="1">
+    <row r="265" spans="1:19" s="175" customFormat="1" ht="16.5" customHeight="1">
       <c r="A265" s="194" t="s">
         <v>2658</v>
       </c>
@@ -44760,7 +44758,7 @@
       <c r="L265" s="169"/>
       <c r="M265" s="168"/>
     </row>
-    <row r="266" spans="1:20" s="175" customFormat="1" ht="16.5" customHeight="1">
+    <row r="266" spans="1:19" s="175" customFormat="1" ht="16.5" customHeight="1">
       <c r="A266" s="194" t="s">
         <v>2660</v>
       </c>
@@ -44789,7 +44787,7 @@
       <c r="L266" s="169"/>
       <c r="M266" s="168"/>
     </row>
-    <row r="267" spans="1:20" s="175" customFormat="1" ht="16.5" customHeight="1">
+    <row r="267" spans="1:19" s="175" customFormat="1" ht="16.5" customHeight="1">
       <c r="A267" s="194" t="s">
         <v>2662</v>
       </c>
@@ -44814,7 +44812,7 @@
       <c r="L267" s="169"/>
       <c r="M267" s="168"/>
     </row>
-    <row r="268" spans="1:20" s="175" customFormat="1" ht="16.5" customHeight="1">
+    <row r="268" spans="1:19" s="175" customFormat="1" ht="16.5" customHeight="1">
       <c r="A268" s="194" t="s">
         <v>2665</v>
       </c>
@@ -44841,7 +44839,7 @@
       <c r="L268" s="169"/>
       <c r="M268" s="168"/>
     </row>
-    <row r="269" spans="1:20" s="175" customFormat="1" ht="16.5" customHeight="1">
+    <row r="269" spans="1:19" s="175" customFormat="1" ht="16.5" customHeight="1">
       <c r="A269" s="194" t="s">
         <v>2667</v>
       </c>
@@ -44868,7 +44866,7 @@
       <c r="L269" s="169"/>
       <c r="M269" s="168"/>
     </row>
-    <row r="270" spans="1:20" s="175" customFormat="1" ht="16.5" customHeight="1">
+    <row r="270" spans="1:19" s="175" customFormat="1" ht="16.5" customHeight="1">
       <c r="A270" s="194" t="s">
         <v>2668</v>
       </c>
@@ -44895,7 +44893,7 @@
       <c r="L270" s="169"/>
       <c r="M270" s="168"/>
     </row>
-    <row r="271" spans="1:20" s="175" customFormat="1" ht="16.5" customHeight="1">
+    <row r="271" spans="1:19" s="175" customFormat="1" ht="16.5" customHeight="1">
       <c r="A271" s="194" t="s">
         <v>2669</v>
       </c>
@@ -44922,7 +44920,7 @@
       <c r="L271" s="169"/>
       <c r="M271" s="168"/>
     </row>
-    <row r="272" spans="1:20" s="175" customFormat="1" ht="16.5" customHeight="1">
+    <row r="272" spans="1:19" s="175" customFormat="1" ht="16.5" customHeight="1">
       <c r="A272" s="194" t="s">
         <v>2670</v>
       </c>
@@ -46265,7 +46263,7 @@
       <c r="L320" s="169"/>
       <c r="M320" s="168"/>
     </row>
-    <row r="321" spans="1:13" s="175" customFormat="1" ht="16.5" customHeight="1">
+    <row r="321" spans="1:19" s="175" customFormat="1" ht="16.5" customHeight="1">
       <c r="A321" s="168" t="s">
         <v>2767</v>
       </c>
@@ -46294,7 +46292,7 @@
       <c r="L321" s="169"/>
       <c r="M321" s="168"/>
     </row>
-    <row r="322" spans="1:13" s="175" customFormat="1" ht="16.5" customHeight="1">
+    <row r="322" spans="1:19" s="175" customFormat="1" ht="16.5" customHeight="1">
       <c r="A322" s="168" t="s">
         <v>2769</v>
       </c>
@@ -46322,8 +46320,26 @@
       <c r="K322" s="169"/>
       <c r="L322" s="169"/>
       <c r="M322" s="168"/>
-    </row>
-    <row r="323" spans="1:13" s="175" customFormat="1" ht="16.5" customHeight="1">
+      <c r="N322" s="175" t="s">
+        <v>3169</v>
+      </c>
+      <c r="O322" s="217" t="s">
+        <v>3169</v>
+      </c>
+      <c r="P322" s="175" t="s">
+        <v>3170</v>
+      </c>
+      <c r="Q322" s="175">
+        <v>1</v>
+      </c>
+      <c r="R322" s="175" t="s">
+        <v>3171</v>
+      </c>
+      <c r="S322" s="175" t="s">
+        <v>3172</v>
+      </c>
+    </row>
+    <row r="323" spans="1:19" s="175" customFormat="1" ht="16.5" customHeight="1">
       <c r="A323" s="168" t="s">
         <v>2771</v>
       </c>
@@ -46352,7 +46368,7 @@
       <c r="L323" s="169"/>
       <c r="M323" s="168"/>
     </row>
-    <row r="324" spans="1:13" s="175" customFormat="1" ht="16.5" customHeight="1">
+    <row r="324" spans="1:19" s="175" customFormat="1" ht="16.5" customHeight="1">
       <c r="A324" s="168" t="s">
         <v>2773</v>
       </c>
@@ -46381,7 +46397,7 @@
       <c r="L324" s="169"/>
       <c r="M324" s="168"/>
     </row>
-    <row r="325" spans="1:13" s="175" customFormat="1" ht="16.5" customHeight="1">
+    <row r="325" spans="1:19" s="175" customFormat="1" ht="16.5" customHeight="1">
       <c r="A325" s="168" t="s">
         <v>2775</v>
       </c>
@@ -46409,8 +46425,26 @@
       <c r="K325" s="169"/>
       <c r="L325" s="169"/>
       <c r="M325" s="168"/>
-    </row>
-    <row r="326" spans="1:13" s="175" customFormat="1" ht="16.5" customHeight="1">
+      <c r="N325" s="175" t="s">
+        <v>3165</v>
+      </c>
+      <c r="O325" s="217" t="s">
+        <v>3165</v>
+      </c>
+      <c r="P325" s="175" t="s">
+        <v>3168</v>
+      </c>
+      <c r="Q325" s="175">
+        <v>1</v>
+      </c>
+      <c r="R325" s="175" t="s">
+        <v>3166</v>
+      </c>
+      <c r="S325" s="175" t="s">
+        <v>3167</v>
+      </c>
+    </row>
+    <row r="326" spans="1:19" s="175" customFormat="1" ht="16.5" customHeight="1">
       <c r="A326" s="168" t="s">
         <v>2777</v>
       </c>
@@ -46437,7 +46471,7 @@
       <c r="L326" s="169"/>
       <c r="M326" s="168"/>
     </row>
-    <row r="327" spans="1:13" s="175" customFormat="1" ht="16.5" customHeight="1">
+    <row r="327" spans="1:19" s="175" customFormat="1" ht="16.5" customHeight="1">
       <c r="A327" s="168" t="s">
         <v>2779</v>
       </c>
@@ -46464,7 +46498,7 @@
       <c r="L327" s="169"/>
       <c r="M327" s="168"/>
     </row>
-    <row r="328" spans="1:13" s="175" customFormat="1" ht="15" customHeight="1">
+    <row r="328" spans="1:19" s="175" customFormat="1" ht="15" customHeight="1">
       <c r="A328" s="168" t="s">
         <v>2781</v>
       </c>
@@ -46493,7 +46527,7 @@
       <c r="L328" s="187"/>
       <c r="M328" s="180"/>
     </row>
-    <row r="329" spans="1:13" s="175" customFormat="1" ht="15.75" customHeight="1">
+    <row r="329" spans="1:19" s="175" customFormat="1" ht="15.75" customHeight="1">
       <c r="A329" s="194" t="s">
         <v>2783</v>
       </c>
@@ -46522,7 +46556,7 @@
       <c r="L329" s="169"/>
       <c r="M329" s="168"/>
     </row>
-    <row r="330" spans="1:13" s="175" customFormat="1" ht="15" customHeight="1">
+    <row r="330" spans="1:19" s="175" customFormat="1" ht="15" customHeight="1">
       <c r="A330" s="194" t="s">
         <v>2785</v>
       </c>
@@ -46551,7 +46585,7 @@
       <c r="L330" s="169"/>
       <c r="M330" s="168"/>
     </row>
-    <row r="331" spans="1:13" s="175" customFormat="1" ht="15" customHeight="1">
+    <row r="331" spans="1:19" s="175" customFormat="1" ht="15" customHeight="1">
       <c r="A331" s="194" t="s">
         <v>2787</v>
       </c>
@@ -46580,7 +46614,7 @@
       <c r="L331" s="169"/>
       <c r="M331" s="168"/>
     </row>
-    <row r="332" spans="1:13" s="175" customFormat="1" ht="15.75" customHeight="1">
+    <row r="332" spans="1:19" s="175" customFormat="1" ht="15.75" customHeight="1">
       <c r="A332" s="194" t="s">
         <v>2789</v>
       </c>
@@ -46609,7 +46643,7 @@
       <c r="L332" s="169"/>
       <c r="M332" s="168"/>
     </row>
-    <row r="333" spans="1:13" s="175" customFormat="1" ht="15.75" customHeight="1">
+    <row r="333" spans="1:19" s="175" customFormat="1" ht="15.75" customHeight="1">
       <c r="A333" s="194" t="s">
         <v>2791</v>
       </c>
@@ -46638,7 +46672,7 @@
       <c r="L333" s="169"/>
       <c r="M333" s="168"/>
     </row>
-    <row r="334" spans="1:13" s="175" customFormat="1" ht="15.75" customHeight="1">
+    <row r="334" spans="1:19" s="175" customFormat="1" ht="15.75" customHeight="1">
       <c r="A334" s="194" t="s">
         <v>2793</v>
       </c>
@@ -46667,7 +46701,7 @@
       <c r="L334" s="169"/>
       <c r="M334" s="168"/>
     </row>
-    <row r="335" spans="1:13" s="175" customFormat="1" ht="15.75" customHeight="1">
+    <row r="335" spans="1:19" s="175" customFormat="1" ht="15.75" customHeight="1">
       <c r="A335" s="194" t="s">
         <v>2794</v>
       </c>
@@ -46696,7 +46730,7 @@
       <c r="L335" s="169"/>
       <c r="M335" s="168"/>
     </row>
-    <row r="336" spans="1:13" s="175" customFormat="1" ht="15.75" customHeight="1">
+    <row r="336" spans="1:19" s="175" customFormat="1" ht="15.75" customHeight="1">
       <c r="A336" s="194" t="s">
         <v>2796</v>
       </c>
@@ -46725,7 +46759,7 @@
       <c r="L336" s="169"/>
       <c r="M336" s="168"/>
     </row>
-    <row r="337" spans="1:13" s="175" customFormat="1" ht="15.75" customHeight="1">
+    <row r="337" spans="1:19" s="175" customFormat="1" ht="15.75" customHeight="1">
       <c r="A337" s="194" t="s">
         <v>2798</v>
       </c>
@@ -46754,7 +46788,7 @@
       <c r="L337" s="169"/>
       <c r="M337" s="168"/>
     </row>
-    <row r="338" spans="1:13" s="175" customFormat="1" ht="15.75" customHeight="1">
+    <row r="338" spans="1:19" s="175" customFormat="1" ht="15.75" customHeight="1">
       <c r="A338" s="194" t="s">
         <v>2800</v>
       </c>
@@ -46781,7 +46815,7 @@
       <c r="L338" s="169"/>
       <c r="M338" s="168"/>
     </row>
-    <row r="339" spans="1:13" s="175" customFormat="1" ht="15.75" customHeight="1">
+    <row r="339" spans="1:19" s="175" customFormat="1" ht="15.75" customHeight="1">
       <c r="A339" s="194" t="s">
         <v>2801</v>
       </c>
@@ -46808,7 +46842,7 @@
       <c r="L339" s="169"/>
       <c r="M339" s="168"/>
     </row>
-    <row r="340" spans="1:13" s="175" customFormat="1" ht="15.75" customHeight="1">
+    <row r="340" spans="1:19" s="175" customFormat="1" ht="15.75" customHeight="1">
       <c r="A340" s="194" t="s">
         <v>2802</v>
       </c>
@@ -46835,7 +46869,7 @@
       <c r="L340" s="169"/>
       <c r="M340" s="168"/>
     </row>
-    <row r="341" spans="1:13" s="175" customFormat="1" ht="15.75" customHeight="1">
+    <row r="341" spans="1:19" s="175" customFormat="1" ht="15.75" customHeight="1">
       <c r="A341" s="194" t="s">
         <v>2804</v>
       </c>
@@ -46862,7 +46896,7 @@
       <c r="L341" s="169"/>
       <c r="M341" s="168"/>
     </row>
-    <row r="342" spans="1:13" s="175" customFormat="1" ht="15.75" customHeight="1">
+    <row r="342" spans="1:19" s="175" customFormat="1" ht="15.75" customHeight="1">
       <c r="A342" s="194" t="s">
         <v>2806</v>
       </c>
@@ -46889,7 +46923,7 @@
       <c r="L342" s="169"/>
       <c r="M342" s="168"/>
     </row>
-    <row r="343" spans="1:13" s="175" customFormat="1" ht="15.75" customHeight="1">
+    <row r="343" spans="1:19" s="175" customFormat="1" ht="15.75" customHeight="1">
       <c r="A343" s="194" t="s">
         <v>2808</v>
       </c>
@@ -46916,7 +46950,7 @@
       <c r="L343" s="169"/>
       <c r="M343" s="168"/>
     </row>
-    <row r="344" spans="1:13" s="175" customFormat="1" ht="15.75" customHeight="1">
+    <row r="344" spans="1:19" s="175" customFormat="1" ht="15.75" customHeight="1">
       <c r="A344" s="194" t="s">
         <v>2810</v>
       </c>
@@ -46945,7 +46979,7 @@
       <c r="L344" s="169"/>
       <c r="M344" s="168"/>
     </row>
-    <row r="345" spans="1:13" s="175" customFormat="1" ht="15.75" customHeight="1">
+    <row r="345" spans="1:19" s="175" customFormat="1" ht="15.75" customHeight="1">
       <c r="A345" s="194" t="s">
         <v>2812</v>
       </c>
@@ -46974,7 +47008,7 @@
       <c r="L345" s="169"/>
       <c r="M345" s="168"/>
     </row>
-    <row r="346" spans="1:13" s="175" customFormat="1" ht="15.75" customHeight="1">
+    <row r="346" spans="1:19" s="175" customFormat="1" ht="15.75" customHeight="1">
       <c r="A346" s="194" t="s">
         <v>2814</v>
       </c>
@@ -47002,8 +47036,26 @@
       <c r="K346" s="169"/>
       <c r="L346" s="169"/>
       <c r="M346" s="168"/>
-    </row>
-    <row r="347" spans="1:13" s="175" customFormat="1" ht="15.75" customHeight="1">
+      <c r="N346" s="175" t="s">
+        <v>3160</v>
+      </c>
+      <c r="O346" s="217" t="s">
+        <v>3160</v>
+      </c>
+      <c r="P346" s="175" t="s">
+        <v>3158</v>
+      </c>
+      <c r="Q346" s="175">
+        <v>1</v>
+      </c>
+      <c r="R346" s="175" t="s">
+        <v>3161</v>
+      </c>
+      <c r="S346" s="175">
+        <v>8.0236099999999997</v>
+      </c>
+    </row>
+    <row r="347" spans="1:19" s="175" customFormat="1" ht="15.75" customHeight="1">
       <c r="A347" s="194" t="s">
         <v>2816</v>
       </c>
@@ -47031,8 +47083,26 @@
       <c r="K347" s="169"/>
       <c r="L347" s="169"/>
       <c r="M347" s="168"/>
-    </row>
-    <row r="348" spans="1:13" s="175" customFormat="1" ht="15.75" customHeight="1">
+      <c r="N347" s="175" t="s">
+        <v>3157</v>
+      </c>
+      <c r="O347" s="217" t="s">
+        <v>3157</v>
+      </c>
+      <c r="P347" s="175" t="s">
+        <v>3158</v>
+      </c>
+      <c r="Q347" s="175">
+        <v>1</v>
+      </c>
+      <c r="R347" s="175" t="s">
+        <v>3159</v>
+      </c>
+      <c r="S347" s="175">
+        <v>402788</v>
+      </c>
+    </row>
+    <row r="348" spans="1:19" s="175" customFormat="1" ht="15.75" customHeight="1">
       <c r="A348" s="194" t="s">
         <v>2818</v>
       </c>
@@ -47061,7 +47131,7 @@
       <c r="L348" s="169"/>
       <c r="M348" s="168"/>
     </row>
-    <row r="349" spans="1:13" s="175" customFormat="1" ht="15.75" customHeight="1">
+    <row r="349" spans="1:19" s="175" customFormat="1" ht="15.75" customHeight="1">
       <c r="A349" s="194" t="s">
         <v>2820</v>
       </c>
@@ -47090,7 +47160,7 @@
       <c r="L349" s="169"/>
       <c r="M349" s="168"/>
     </row>
-    <row r="350" spans="1:13" s="175" customFormat="1" ht="15.75" customHeight="1">
+    <row r="350" spans="1:19" s="175" customFormat="1" ht="15.75" customHeight="1">
       <c r="A350" s="194" t="s">
         <v>2822</v>
       </c>
@@ -47115,7 +47185,7 @@
       <c r="L350" s="169"/>
       <c r="M350" s="168"/>
     </row>
-    <row r="351" spans="1:13" s="175" customFormat="1" ht="15.75" customHeight="1">
+    <row r="351" spans="1:19" s="175" customFormat="1" ht="15.75" customHeight="1">
       <c r="A351" s="194" t="s">
         <v>2824</v>
       </c>
@@ -47140,7 +47210,7 @@
       <c r="L351" s="169"/>
       <c r="M351" s="168"/>
     </row>
-    <row r="352" spans="1:13" s="175" customFormat="1" ht="15.75" customHeight="1">
+    <row r="352" spans="1:19" s="175" customFormat="1" ht="15.75" customHeight="1">
       <c r="A352" s="194" t="s">
         <v>2826</v>
       </c>
@@ -47169,7 +47239,7 @@
       <c r="L352" s="169"/>
       <c r="M352" s="168"/>
     </row>
-    <row r="353" spans="1:13" s="175" customFormat="1" ht="15.75" customHeight="1">
+    <row r="353" spans="1:19" s="175" customFormat="1" ht="15.75" customHeight="1">
       <c r="A353" s="194" t="s">
         <v>2828</v>
       </c>
@@ -47196,7 +47266,7 @@
       <c r="L353" s="169"/>
       <c r="M353" s="168"/>
     </row>
-    <row r="354" spans="1:13" s="175" customFormat="1" ht="15.75" customHeight="1">
+    <row r="354" spans="1:19" s="175" customFormat="1" ht="15.75" customHeight="1">
       <c r="A354" s="194" t="s">
         <v>2830</v>
       </c>
@@ -47222,8 +47292,26 @@
       <c r="K354" s="169"/>
       <c r="L354" s="169"/>
       <c r="M354" s="168"/>
-    </row>
-    <row r="355" spans="1:13" s="175" customFormat="1" ht="15.75" customHeight="1">
+      <c r="N354" s="175" t="s">
+        <v>3162</v>
+      </c>
+      <c r="O354" s="217" t="s">
+        <v>3162</v>
+      </c>
+      <c r="P354" s="175" t="s">
+        <v>3163</v>
+      </c>
+      <c r="Q354" s="175">
+        <v>1</v>
+      </c>
+      <c r="R354" s="175" t="s">
+        <v>3164</v>
+      </c>
+      <c r="S354" s="175">
+        <v>659452</v>
+      </c>
+    </row>
+    <row r="355" spans="1:19" s="175" customFormat="1" ht="15.75" customHeight="1">
       <c r="A355" s="194" t="s">
         <v>2832</v>
       </c>
@@ -47250,7 +47338,7 @@
       <c r="L355" s="169"/>
       <c r="M355" s="168"/>
     </row>
-    <row r="356" spans="1:13" s="175" customFormat="1" ht="15.75" customHeight="1">
+    <row r="356" spans="1:19" s="175" customFormat="1" ht="15.75" customHeight="1">
       <c r="A356" s="194" t="s">
         <v>2834</v>
       </c>
@@ -47277,7 +47365,7 @@
       <c r="L356" s="169"/>
       <c r="M356" s="168"/>
     </row>
-    <row r="357" spans="1:13" s="175" customFormat="1" ht="15.75" customHeight="1">
+    <row r="357" spans="1:19" s="175" customFormat="1" ht="15.75" customHeight="1">
       <c r="A357" s="194" t="s">
         <v>2836</v>
       </c>
@@ -47304,7 +47392,7 @@
       <c r="L357" s="169"/>
       <c r="M357" s="168"/>
     </row>
-    <row r="358" spans="1:13" s="175" customFormat="1" ht="15.75" customHeight="1">
+    <row r="358" spans="1:19" s="175" customFormat="1" ht="15.75" customHeight="1">
       <c r="A358" s="194" t="s">
         <v>2838</v>
       </c>
@@ -47331,7 +47419,7 @@
       <c r="L358" s="169"/>
       <c r="M358" s="168"/>
     </row>
-    <row r="359" spans="1:13" s="175" customFormat="1" ht="15.75" customHeight="1">
+    <row r="359" spans="1:19" s="175" customFormat="1" ht="15.75" customHeight="1">
       <c r="A359" s="194" t="s">
         <v>2840</v>
       </c>
@@ -47358,7 +47446,7 @@
       <c r="L359" s="169"/>
       <c r="M359" s="168"/>
     </row>
-    <row r="360" spans="1:13" s="175" customFormat="1" ht="15.75" customHeight="1">
+    <row r="360" spans="1:19" s="175" customFormat="1" ht="15.75" customHeight="1">
       <c r="A360" s="194" t="s">
         <v>2842</v>
       </c>
@@ -47385,7 +47473,7 @@
       <c r="L360" s="169"/>
       <c r="M360" s="168"/>
     </row>
-    <row r="361" spans="1:13" s="175" customFormat="1" ht="15.75" customHeight="1">
+    <row r="361" spans="1:19" s="175" customFormat="1" ht="15.75" customHeight="1">
       <c r="A361" s="194" t="s">
         <v>2843</v>
       </c>
@@ -47414,7 +47502,7 @@
       <c r="L361" s="169"/>
       <c r="M361" s="168"/>
     </row>
-    <row r="362" spans="1:13" s="175" customFormat="1" ht="15.75" customHeight="1">
+    <row r="362" spans="1:19" s="175" customFormat="1" ht="15.75" customHeight="1">
       <c r="A362" s="194" t="s">
         <v>2845</v>
       </c>
@@ -47441,7 +47529,7 @@
       <c r="L362" s="169"/>
       <c r="M362" s="168"/>
     </row>
-    <row r="363" spans="1:13" s="175" customFormat="1" ht="15.75" customHeight="1">
+    <row r="363" spans="1:19" s="175" customFormat="1" ht="15.75" customHeight="1">
       <c r="A363" s="194" t="s">
         <v>2848</v>
       </c>
@@ -47468,7 +47556,7 @@
       <c r="L363" s="169"/>
       <c r="M363" s="168"/>
     </row>
-    <row r="364" spans="1:13" s="175" customFormat="1" ht="15.75" customHeight="1">
+    <row r="364" spans="1:19" s="175" customFormat="1" ht="15.75" customHeight="1">
       <c r="A364" s="194" t="s">
         <v>2849</v>
       </c>
@@ -47495,7 +47583,7 @@
       <c r="L364" s="169"/>
       <c r="M364" s="168"/>
     </row>
-    <row r="365" spans="1:13" s="175" customFormat="1" ht="15.75" customHeight="1">
+    <row r="365" spans="1:19" s="175" customFormat="1" ht="15.75" customHeight="1">
       <c r="A365" s="209" t="s">
         <v>2850</v>
       </c>
@@ -47522,7 +47610,7 @@
       <c r="L365" s="187"/>
       <c r="M365" s="180"/>
     </row>
-    <row r="366" spans="1:13" s="175" customFormat="1" ht="16.5" customHeight="1">
+    <row r="366" spans="1:19" s="175" customFormat="1" ht="16.5" customHeight="1">
       <c r="A366" s="168" t="s">
         <v>2852</v>
       </c>
@@ -47549,7 +47637,7 @@
       <c r="L366" s="169"/>
       <c r="M366" s="168"/>
     </row>
-    <row r="367" spans="1:13" s="175" customFormat="1" ht="16.5" customHeight="1">
+    <row r="367" spans="1:19" s="175" customFormat="1" ht="16.5" customHeight="1">
       <c r="A367" s="168" t="s">
         <v>2853</v>
       </c>
@@ -47576,7 +47664,7 @@
       <c r="L367" s="169"/>
       <c r="M367" s="168"/>
     </row>
-    <row r="368" spans="1:13" s="175" customFormat="1" ht="16.5" customHeight="1">
+    <row r="368" spans="1:19" s="175" customFormat="1" ht="16.5" customHeight="1">
       <c r="A368" s="168" t="s">
         <v>2855</v>
       </c>
@@ -49377,7 +49465,7 @@
       <c r="L432" s="169"/>
       <c r="M432" s="168"/>
     </row>
-    <row r="433" spans="1:13" s="175" customFormat="1" ht="16.5" customHeight="1">
+    <row r="433" spans="1:15" s="175" customFormat="1" ht="16.5" customHeight="1">
       <c r="A433" s="168" t="s">
         <v>2983</v>
       </c>
@@ -49402,7 +49490,7 @@
       <c r="L433" s="169"/>
       <c r="M433" s="168"/>
     </row>
-    <row r="434" spans="1:13" s="175" customFormat="1" ht="16.5" customHeight="1">
+    <row r="434" spans="1:15" s="175" customFormat="1" ht="16.5" customHeight="1">
       <c r="A434" s="168" t="s">
         <v>2985</v>
       </c>
@@ -49427,7 +49515,7 @@
       <c r="L434" s="169"/>
       <c r="M434" s="168"/>
     </row>
-    <row r="435" spans="1:13" s="175" customFormat="1" ht="16.5" customHeight="1">
+    <row r="435" spans="1:15" s="175" customFormat="1" ht="16.5" customHeight="1">
       <c r="A435" s="168" t="s">
         <v>2987</v>
       </c>
@@ -49452,7 +49540,7 @@
       <c r="L435" s="169"/>
       <c r="M435" s="168"/>
     </row>
-    <row r="436" spans="1:13" s="175" customFormat="1" ht="16.5" customHeight="1">
+    <row r="436" spans="1:15" s="175" customFormat="1" ht="16.5" customHeight="1">
       <c r="A436" s="168" t="s">
         <v>2989</v>
       </c>
@@ -49477,7 +49565,7 @@
       <c r="L436" s="169"/>
       <c r="M436" s="168"/>
     </row>
-    <row r="437" spans="1:13" s="175" customFormat="1" ht="16.5" customHeight="1">
+    <row r="437" spans="1:15" s="175" customFormat="1" ht="16.5" customHeight="1">
       <c r="A437" s="168" t="s">
         <v>2991</v>
       </c>
@@ -49504,7 +49592,7 @@
       <c r="L437" s="169"/>
       <c r="M437" s="168"/>
     </row>
-    <row r="438" spans="1:13" s="175" customFormat="1" ht="16.5" customHeight="1">
+    <row r="438" spans="1:15" s="175" customFormat="1" ht="16.5" customHeight="1">
       <c r="A438" s="168" t="s">
         <v>2992</v>
       </c>
@@ -49531,7 +49619,7 @@
       <c r="L438" s="169"/>
       <c r="M438" s="168"/>
     </row>
-    <row r="439" spans="1:13" s="175" customFormat="1" ht="16.5" customHeight="1">
+    <row r="439" spans="1:15" s="175" customFormat="1" ht="16.5" customHeight="1">
       <c r="A439" s="168" t="s">
         <v>2993</v>
       </c>
@@ -49560,7 +49648,7 @@
       <c r="L439" s="169"/>
       <c r="M439" s="168"/>
     </row>
-    <row r="440" spans="1:13" s="175" customFormat="1" ht="16.5" customHeight="1">
+    <row r="440" spans="1:15" s="175" customFormat="1" ht="16.5" customHeight="1">
       <c r="A440" s="168" t="s">
         <v>2994</v>
       </c>
@@ -49589,7 +49677,7 @@
       <c r="L440" s="169"/>
       <c r="M440" s="168"/>
     </row>
-    <row r="441" spans="1:13" s="175" customFormat="1" ht="16.5" customHeight="1">
+    <row r="441" spans="1:15" s="175" customFormat="1" ht="16.5" customHeight="1">
       <c r="A441" s="168" t="s">
         <v>2995</v>
       </c>
@@ -49616,7 +49704,7 @@
       <c r="L441" s="169"/>
       <c r="M441" s="168"/>
     </row>
-    <row r="442" spans="1:13" s="175" customFormat="1" ht="16.5" customHeight="1">
+    <row r="442" spans="1:15" s="175" customFormat="1" ht="16.5" customHeight="1">
       <c r="A442" s="168" t="s">
         <v>2996</v>
       </c>
@@ -49643,7 +49731,7 @@
       <c r="L442" s="169"/>
       <c r="M442" s="168"/>
     </row>
-    <row r="443" spans="1:13" s="175" customFormat="1" ht="16.5" customHeight="1">
+    <row r="443" spans="1:15" s="175" customFormat="1" ht="16.5" customHeight="1">
       <c r="A443" s="168" t="s">
         <v>2997</v>
       </c>
@@ -49670,7 +49758,7 @@
       <c r="L443" s="169"/>
       <c r="M443" s="168"/>
     </row>
-    <row r="444" spans="1:13" s="175" customFormat="1" ht="16.5" customHeight="1">
+    <row r="444" spans="1:15" s="175" customFormat="1" ht="16.5" customHeight="1">
       <c r="A444" s="168" t="s">
         <v>2999</v>
       </c>
@@ -49695,7 +49783,7 @@
       <c r="L444" s="169"/>
       <c r="M444" s="168"/>
     </row>
-    <row r="445" spans="1:13" s="175" customFormat="1" ht="16.5" customHeight="1">
+    <row r="445" spans="1:15" s="175" customFormat="1" ht="16.5" customHeight="1">
       <c r="A445" s="168" t="s">
         <v>3001</v>
       </c>
@@ -49720,7 +49808,7 @@
       <c r="L445" s="169"/>
       <c r="M445" s="168"/>
     </row>
-    <row r="446" spans="1:13" s="175" customFormat="1" ht="16.5" customHeight="1">
+    <row r="446" spans="1:15" s="175" customFormat="1" ht="16.5" customHeight="1">
       <c r="A446" s="168" t="s">
         <v>3003</v>
       </c>
@@ -49747,7 +49835,7 @@
       <c r="L446" s="169"/>
       <c r="M446" s="168"/>
     </row>
-    <row r="447" spans="1:13" s="175" customFormat="1" ht="16.5" customHeight="1">
+    <row r="447" spans="1:15" s="175" customFormat="1" ht="16.5" customHeight="1">
       <c r="A447" s="168" t="s">
         <v>3005</v>
       </c>
@@ -49771,8 +49859,14 @@
       <c r="K447" s="169"/>
       <c r="L447" s="169"/>
       <c r="M447" s="168"/>
-    </row>
-    <row r="448" spans="1:13" s="175" customFormat="1" ht="16.5" customHeight="1">
+      <c r="N447" s="175" t="s">
+        <v>3178</v>
+      </c>
+      <c r="O447" s="217" t="s">
+        <v>3178</v>
+      </c>
+    </row>
+    <row r="448" spans="1:15" s="175" customFormat="1" ht="16.5" customHeight="1">
       <c r="A448" s="168" t="s">
         <v>3006</v>
       </c>
@@ -50194,11 +50288,11 @@
       <c r="K462" s="169"/>
       <c r="L462" s="169"/>
       <c r="M462" s="168"/>
-      <c r="N462" s="217" t="s">
-        <v>3163</v>
+      <c r="N462" s="175" t="s">
+        <v>3153</v>
       </c>
       <c r="O462" s="217" t="s">
-        <v>3163</v>
+        <v>3153</v>
       </c>
     </row>
     <row r="463" spans="1:15" s="175" customFormat="1" ht="16.5" customHeight="1">
@@ -50227,6 +50321,12 @@
       <c r="K463" s="169"/>
       <c r="L463" s="169"/>
       <c r="M463" s="168"/>
+      <c r="N463" s="175" t="s">
+        <v>3177</v>
+      </c>
+      <c r="O463" s="217" t="s">
+        <v>3177</v>
+      </c>
     </row>
     <row r="464" spans="1:15" s="175" customFormat="1" ht="16.5" customHeight="1">
       <c r="A464" s="168" t="s">
@@ -50256,7 +50356,7 @@
       <c r="L464" s="169"/>
       <c r="M464" s="168"/>
     </row>
-    <row r="465" spans="1:15" s="175" customFormat="1" ht="16.5" customHeight="1">
+    <row r="465" spans="1:19" s="175" customFormat="1" ht="16.5" customHeight="1">
       <c r="A465" s="168" t="s">
         <v>3040</v>
       </c>
@@ -50284,7 +50384,7 @@
       <c r="L465" s="169"/>
       <c r="M465" s="168"/>
     </row>
-    <row r="466" spans="1:15" s="175" customFormat="1" ht="16.5" customHeight="1">
+    <row r="466" spans="1:19" s="175" customFormat="1" ht="16.5" customHeight="1">
       <c r="A466" s="168" t="s">
         <v>3042</v>
       </c>
@@ -50313,7 +50413,7 @@
       <c r="L466" s="169"/>
       <c r="M466" s="168"/>
     </row>
-    <row r="467" spans="1:15" s="175" customFormat="1" ht="16.5" customHeight="1">
+    <row r="467" spans="1:19" s="175" customFormat="1" ht="16.5" customHeight="1">
       <c r="A467" s="168" t="s">
         <v>3044</v>
       </c>
@@ -50340,7 +50440,7 @@
       <c r="L467" s="169"/>
       <c r="M467" s="168"/>
     </row>
-    <row r="468" spans="1:15" s="175" customFormat="1" ht="16.5" customHeight="1">
+    <row r="468" spans="1:19" s="175" customFormat="1" ht="16.5" customHeight="1">
       <c r="A468" s="168" t="s">
         <v>3045</v>
       </c>
@@ -50367,7 +50467,7 @@
       <c r="L468" s="169"/>
       <c r="M468" s="168"/>
     </row>
-    <row r="469" spans="1:15" s="175" customFormat="1" ht="16.5" customHeight="1">
+    <row r="469" spans="1:19" s="175" customFormat="1" ht="16.5" customHeight="1">
       <c r="A469" s="168" t="s">
         <v>3046</v>
       </c>
@@ -50394,7 +50494,7 @@
       <c r="L469" s="169"/>
       <c r="M469" s="168"/>
     </row>
-    <row r="470" spans="1:15" s="175" customFormat="1" ht="16.5" customHeight="1">
+    <row r="470" spans="1:19" s="175" customFormat="1" ht="16.5" customHeight="1">
       <c r="A470" s="168" t="s">
         <v>3048</v>
       </c>
@@ -50420,8 +50520,26 @@
       <c r="K470" s="169"/>
       <c r="L470" s="169"/>
       <c r="M470" s="168"/>
-    </row>
-    <row r="471" spans="1:15" s="175" customFormat="1" ht="16.5" customHeight="1">
+      <c r="N470" s="175" t="s">
+        <v>3173</v>
+      </c>
+      <c r="O470" s="217" t="s">
+        <v>3173</v>
+      </c>
+      <c r="P470" s="175" t="s">
+        <v>3174</v>
+      </c>
+      <c r="Q470" s="175">
+        <v>1</v>
+      </c>
+      <c r="R470" s="175" t="s">
+        <v>3175</v>
+      </c>
+      <c r="S470" s="175" t="s">
+        <v>3176</v>
+      </c>
+    </row>
+    <row r="471" spans="1:19" s="175" customFormat="1" ht="16.5" customHeight="1">
       <c r="A471" s="168" t="s">
         <v>3050</v>
       </c>
@@ -50448,7 +50566,7 @@
       <c r="L471" s="169"/>
       <c r="M471" s="168"/>
     </row>
-    <row r="472" spans="1:15" s="175" customFormat="1" ht="16.5" customHeight="1">
+    <row r="472" spans="1:19" s="175" customFormat="1" ht="16.5" customHeight="1">
       <c r="A472" s="168" t="s">
         <v>3053</v>
       </c>
@@ -50474,14 +50592,14 @@
       <c r="K472" s="169"/>
       <c r="L472" s="169"/>
       <c r="M472" s="168"/>
-      <c r="N472" s="217" t="s">
-        <v>3164</v>
+      <c r="N472" s="175" t="s">
+        <v>3154</v>
       </c>
       <c r="O472" s="217" t="s">
-        <v>3164</v>
-      </c>
-    </row>
-    <row r="473" spans="1:15" s="175" customFormat="1" ht="16.5" customHeight="1">
+        <v>3154</v>
+      </c>
+    </row>
+    <row r="473" spans="1:19" s="175" customFormat="1" ht="16.5" customHeight="1">
       <c r="A473" s="168" t="s">
         <v>3055</v>
       </c>
@@ -50508,7 +50626,7 @@
       <c r="L473" s="169"/>
       <c r="M473" s="168"/>
     </row>
-    <row r="474" spans="1:15" s="175" customFormat="1" ht="16.5" customHeight="1">
+    <row r="474" spans="1:19" s="175" customFormat="1" ht="16.5" customHeight="1">
       <c r="A474" s="168" t="s">
         <v>3058</v>
       </c>
@@ -50535,7 +50653,7 @@
       <c r="L474" s="169"/>
       <c r="M474" s="168"/>
     </row>
-    <row r="475" spans="1:15" s="175" customFormat="1" ht="16.5" customHeight="1">
+    <row r="475" spans="1:19" s="175" customFormat="1" ht="16.5" customHeight="1">
       <c r="A475" s="168" t="s">
         <v>3059</v>
       </c>
@@ -50560,7 +50678,7 @@
       <c r="L475" s="169"/>
       <c r="M475" s="168"/>
     </row>
-    <row r="476" spans="1:15" s="175" customFormat="1" ht="16.5" customHeight="1">
+    <row r="476" spans="1:19" s="175" customFormat="1" ht="16.5" customHeight="1">
       <c r="A476" s="168" t="s">
         <v>3061</v>
       </c>
@@ -50586,14 +50704,14 @@
       <c r="K476" s="169"/>
       <c r="L476" s="169"/>
       <c r="M476" s="168"/>
-      <c r="N476" s="217" t="s">
-        <v>3166</v>
+      <c r="N476" s="175" t="s">
+        <v>3156</v>
       </c>
       <c r="O476" s="217" t="s">
-        <v>3166</v>
-      </c>
-    </row>
-    <row r="477" spans="1:15" s="175" customFormat="1" ht="16.5" customHeight="1">
+        <v>3156</v>
+      </c>
+    </row>
+    <row r="477" spans="1:19" s="175" customFormat="1" ht="16.5" customHeight="1">
       <c r="A477" s="168" t="s">
         <v>3063</v>
       </c>
@@ -50620,7 +50738,7 @@
       <c r="L477" s="169"/>
       <c r="M477" s="168"/>
     </row>
-    <row r="478" spans="1:15" s="175" customFormat="1" ht="16.5" customHeight="1">
+    <row r="478" spans="1:19" s="175" customFormat="1" ht="16.5" customHeight="1">
       <c r="A478" s="168" t="s">
         <v>3064</v>
       </c>
@@ -50648,10 +50766,14 @@
       <c r="K478" s="169"/>
       <c r="L478" s="169"/>
       <c r="M478" s="168"/>
-      <c r="N478" s="217"/>
-      <c r="O478" s="217"/>
-    </row>
-    <row r="479" spans="1:15" s="175" customFormat="1" ht="16.5" customHeight="1">
+      <c r="N478" s="175" t="s">
+        <v>3139</v>
+      </c>
+      <c r="O478" s="217" t="s">
+        <v>3139</v>
+      </c>
+    </row>
+    <row r="479" spans="1:19" s="175" customFormat="1" ht="16.5" customHeight="1">
       <c r="A479" s="168" t="s">
         <v>3066</v>
       </c>
@@ -50678,7 +50800,7 @@
       <c r="L479" s="169"/>
       <c r="M479" s="168"/>
     </row>
-    <row r="480" spans="1:15" s="175" customFormat="1" ht="16.5" customHeight="1">
+    <row r="480" spans="1:19" s="175" customFormat="1" ht="16.5" customHeight="1">
       <c r="A480" s="168" t="s">
         <v>3068</v>
       </c>
@@ -50704,11 +50826,11 @@
       <c r="K480" s="169"/>
       <c r="L480" s="169"/>
       <c r="M480" s="168"/>
-      <c r="N480" s="217" t="s">
-        <v>3165</v>
+      <c r="N480" s="175" t="s">
+        <v>3155</v>
       </c>
       <c r="O480" s="217" t="s">
-        <v>3165</v>
+        <v>3155</v>
       </c>
     </row>
     <row r="481" spans="1:13" s="175" customFormat="1" ht="16.5" customHeight="1">

--- a/order book.xlsx
+++ b/order book.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7398" uniqueCount="3179">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7418" uniqueCount="3194">
   <si>
     <t>* 부가세(VAT) 포함 금액 기재 / 서브원 외에는 물품 "사진" 필수</t>
   </si>
@@ -9613,6 +9613,64 @@
   </si>
   <si>
     <t>o</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>o</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>o</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>O</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>o</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>abcam</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>20 uL</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ab92536</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Lot No.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>ThermoFisher</t>
+  </si>
+  <si>
+    <t>M30550</t>
+  </si>
+  <si>
+    <t>o</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>8/13</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>dd</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>sdfg</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>46eoier</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -9933,7 +9991,7 @@
       <charset val="129"/>
     </font>
   </fonts>
-  <fills count="12">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -9991,12 +10049,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFE6F7E6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -10481,7 +10533,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="242">
+  <cellXfs count="241">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -11125,9 +11177,6 @@
     <xf numFmtId="3" fontId="5" fillId="0" borderId="19" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="11" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="7" borderId="34" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
@@ -11521,174 +11570,174 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:19" ht="21.75" customHeight="1">
-      <c r="A1" s="221" t="s">
+      <c r="A1" s="220" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="222"/>
-      <c r="C1" s="223"/>
-      <c r="D1" s="223"/>
-      <c r="E1" s="223"/>
-      <c r="F1" s="223"/>
-      <c r="G1" s="223"/>
-      <c r="H1" s="223"/>
-      <c r="I1" s="223"/>
-      <c r="J1" s="224"/>
-      <c r="K1" s="222"/>
-      <c r="L1" s="222"/>
-      <c r="M1" s="223"/>
+      <c r="B1" s="221"/>
+      <c r="C1" s="222"/>
+      <c r="D1" s="222"/>
+      <c r="E1" s="222"/>
+      <c r="F1" s="222"/>
+      <c r="G1" s="222"/>
+      <c r="H1" s="222"/>
+      <c r="I1" s="222"/>
+      <c r="J1" s="223"/>
+      <c r="K1" s="221"/>
+      <c r="L1" s="221"/>
+      <c r="M1" s="222"/>
     </row>
     <row r="2" spans="1:19">
-      <c r="A2" s="239" t="s">
+      <c r="A2" s="238" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="240"/>
-      <c r="C2" s="240"/>
-      <c r="D2" s="240"/>
-      <c r="E2" s="240"/>
-      <c r="F2" s="240"/>
-      <c r="G2" s="240"/>
-      <c r="H2" s="240"/>
-      <c r="I2" s="240"/>
-      <c r="J2" s="240"/>
-      <c r="K2" s="240"/>
-      <c r="L2" s="240"/>
-      <c r="M2" s="241"/>
+      <c r="B2" s="239"/>
+      <c r="C2" s="239"/>
+      <c r="D2" s="239"/>
+      <c r="E2" s="239"/>
+      <c r="F2" s="239"/>
+      <c r="G2" s="239"/>
+      <c r="H2" s="239"/>
+      <c r="I2" s="239"/>
+      <c r="J2" s="239"/>
+      <c r="K2" s="239"/>
+      <c r="L2" s="239"/>
+      <c r="M2" s="240"/>
     </row>
     <row r="3" spans="1:19" ht="19.5" customHeight="1">
-      <c r="A3" s="236" t="s">
+      <c r="A3" s="235" t="s">
         <v>2</v>
       </c>
-      <c r="B3" s="237"/>
-      <c r="C3" s="237"/>
-      <c r="D3" s="237"/>
-      <c r="E3" s="237"/>
-      <c r="F3" s="237"/>
-      <c r="G3" s="237"/>
-      <c r="H3" s="237"/>
-      <c r="I3" s="237"/>
-      <c r="J3" s="237"/>
-      <c r="K3" s="237"/>
-      <c r="L3" s="237"/>
-      <c r="M3" s="237"/>
+      <c r="B3" s="236"/>
+      <c r="C3" s="236"/>
+      <c r="D3" s="236"/>
+      <c r="E3" s="236"/>
+      <c r="F3" s="236"/>
+      <c r="G3" s="236"/>
+      <c r="H3" s="236"/>
+      <c r="I3" s="236"/>
+      <c r="J3" s="236"/>
+      <c r="K3" s="236"/>
+      <c r="L3" s="236"/>
+      <c r="M3" s="236"/>
     </row>
     <row r="4" spans="1:19" s="5" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A4" s="233" t="s">
+      <c r="A4" s="232" t="s">
         <v>3</v>
       </c>
-      <c r="B4" s="234"/>
-      <c r="C4" s="234"/>
-      <c r="D4" s="234"/>
-      <c r="E4" s="234"/>
-      <c r="F4" s="234"/>
-      <c r="G4" s="234"/>
-      <c r="H4" s="234"/>
-      <c r="I4" s="234"/>
-      <c r="J4" s="234"/>
-      <c r="K4" s="234"/>
-      <c r="L4" s="234"/>
-      <c r="M4" s="235"/>
+      <c r="B4" s="233"/>
+      <c r="C4" s="233"/>
+      <c r="D4" s="233"/>
+      <c r="E4" s="233"/>
+      <c r="F4" s="233"/>
+      <c r="G4" s="233"/>
+      <c r="H4" s="233"/>
+      <c r="I4" s="233"/>
+      <c r="J4" s="233"/>
+      <c r="K4" s="233"/>
+      <c r="L4" s="233"/>
+      <c r="M4" s="234"/>
     </row>
     <row r="5" spans="1:19" s="5" customFormat="1" ht="19.5" customHeight="1">
-      <c r="A5" s="225" t="s">
+      <c r="A5" s="224" t="s">
         <v>4</v>
       </c>
-      <c r="B5" s="226"/>
-      <c r="C5" s="226"/>
-      <c r="D5" s="226"/>
-      <c r="E5" s="226"/>
-      <c r="F5" s="226"/>
-      <c r="G5" s="226"/>
-      <c r="H5" s="226"/>
-      <c r="I5" s="226"/>
-      <c r="J5" s="226"/>
-      <c r="K5" s="226"/>
-      <c r="L5" s="226"/>
-      <c r="M5" s="227"/>
+      <c r="B5" s="225"/>
+      <c r="C5" s="225"/>
+      <c r="D5" s="225"/>
+      <c r="E5" s="225"/>
+      <c r="F5" s="225"/>
+      <c r="G5" s="225"/>
+      <c r="H5" s="225"/>
+      <c r="I5" s="225"/>
+      <c r="J5" s="225"/>
+      <c r="K5" s="225"/>
+      <c r="L5" s="225"/>
+      <c r="M5" s="226"/>
     </row>
     <row r="6" spans="1:19" s="5" customFormat="1" ht="21.75" customHeight="1" thickBot="1">
-      <c r="A6" s="229" t="s">
+      <c r="A6" s="228" t="s">
         <v>5</v>
       </c>
-      <c r="B6" s="230"/>
-      <c r="C6" s="230"/>
-      <c r="D6" s="230"/>
-      <c r="E6" s="230"/>
-      <c r="F6" s="230"/>
-      <c r="G6" s="230"/>
-      <c r="H6" s="230"/>
-      <c r="I6" s="230"/>
-      <c r="J6" s="230"/>
-      <c r="K6" s="230"/>
-      <c r="L6" s="230"/>
-      <c r="M6" s="231"/>
+      <c r="B6" s="229"/>
+      <c r="C6" s="229"/>
+      <c r="D6" s="229"/>
+      <c r="E6" s="229"/>
+      <c r="F6" s="229"/>
+      <c r="G6" s="229"/>
+      <c r="H6" s="229"/>
+      <c r="I6" s="229"/>
+      <c r="J6" s="229"/>
+      <c r="K6" s="229"/>
+      <c r="L6" s="229"/>
+      <c r="M6" s="230"/>
     </row>
     <row r="7" spans="1:19" s="5" customFormat="1" ht="25.5" hidden="1" customHeight="1">
-      <c r="A7" s="238" t="s">
+      <c r="A7" s="237" t="s">
         <v>6</v>
       </c>
-      <c r="B7" s="219"/>
-      <c r="C7" s="219"/>
-      <c r="D7" s="219"/>
-      <c r="E7" s="219"/>
-      <c r="F7" s="219"/>
-      <c r="G7" s="219"/>
-      <c r="H7" s="219"/>
-      <c r="I7" s="219"/>
-      <c r="J7" s="219"/>
-      <c r="K7" s="219"/>
-      <c r="L7" s="219"/>
-      <c r="M7" s="219"/>
+      <c r="B7" s="218"/>
+      <c r="C7" s="218"/>
+      <c r="D7" s="218"/>
+      <c r="E7" s="218"/>
+      <c r="F7" s="218"/>
+      <c r="G7" s="218"/>
+      <c r="H7" s="218"/>
+      <c r="I7" s="218"/>
+      <c r="J7" s="218"/>
+      <c r="K7" s="218"/>
+      <c r="L7" s="218"/>
+      <c r="M7" s="218"/>
     </row>
     <row r="8" spans="1:19" s="5" customFormat="1" ht="41.25" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A8" s="228" t="s">
+      <c r="A8" s="227" t="s">
         <v>7</v>
       </c>
-      <c r="B8" s="219"/>
-      <c r="C8" s="219"/>
-      <c r="D8" s="219"/>
-      <c r="E8" s="219"/>
-      <c r="F8" s="219"/>
-      <c r="G8" s="219"/>
-      <c r="H8" s="219"/>
-      <c r="I8" s="219"/>
-      <c r="J8" s="219"/>
-      <c r="K8" s="219"/>
-      <c r="L8" s="219"/>
-      <c r="M8" s="219"/>
+      <c r="B8" s="218"/>
+      <c r="C8" s="218"/>
+      <c r="D8" s="218"/>
+      <c r="E8" s="218"/>
+      <c r="F8" s="218"/>
+      <c r="G8" s="218"/>
+      <c r="H8" s="218"/>
+      <c r="I8" s="218"/>
+      <c r="J8" s="218"/>
+      <c r="K8" s="218"/>
+      <c r="L8" s="218"/>
+      <c r="M8" s="218"/>
     </row>
     <row r="9" spans="1:19" s="5" customFormat="1" ht="28.5" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A9" s="232" t="s">
+      <c r="A9" s="231" t="s">
         <v>8</v>
       </c>
-      <c r="B9" s="219"/>
-      <c r="C9" s="219"/>
-      <c r="D9" s="219"/>
-      <c r="E9" s="219"/>
-      <c r="F9" s="219"/>
-      <c r="G9" s="219"/>
-      <c r="H9" s="219"/>
-      <c r="I9" s="219"/>
-      <c r="J9" s="219"/>
-      <c r="K9" s="219"/>
-      <c r="L9" s="219"/>
-      <c r="M9" s="219"/>
+      <c r="B9" s="218"/>
+      <c r="C9" s="218"/>
+      <c r="D9" s="218"/>
+      <c r="E9" s="218"/>
+      <c r="F9" s="218"/>
+      <c r="G9" s="218"/>
+      <c r="H9" s="218"/>
+      <c r="I9" s="218"/>
+      <c r="J9" s="218"/>
+      <c r="K9" s="218"/>
+      <c r="L9" s="218"/>
+      <c r="M9" s="218"/>
     </row>
     <row r="10" spans="1:19" s="5" customFormat="1" ht="21.75" customHeight="1" thickTop="1" thickBot="1">
-      <c r="A10" s="218" t="s">
+      <c r="A10" s="217" t="s">
         <v>9</v>
       </c>
-      <c r="B10" s="219"/>
-      <c r="C10" s="219"/>
-      <c r="D10" s="219"/>
-      <c r="E10" s="219"/>
-      <c r="F10" s="219"/>
-      <c r="G10" s="219"/>
-      <c r="H10" s="219"/>
-      <c r="I10" s="219"/>
-      <c r="J10" s="219"/>
-      <c r="K10" s="219"/>
-      <c r="L10" s="219"/>
-      <c r="M10" s="220"/>
+      <c r="B10" s="218"/>
+      <c r="C10" s="218"/>
+      <c r="D10" s="218"/>
+      <c r="E10" s="218"/>
+      <c r="F10" s="218"/>
+      <c r="G10" s="218"/>
+      <c r="H10" s="218"/>
+      <c r="I10" s="218"/>
+      <c r="J10" s="218"/>
+      <c r="K10" s="218"/>
+      <c r="L10" s="218"/>
+      <c r="M10" s="219"/>
     </row>
     <row r="11" spans="1:19" s="5" customFormat="1" ht="17.25" customHeight="1">
       <c r="A11" s="2" t="s">
@@ -37350,109 +37399,109 @@
     <col min="21" max="16384" width="7.625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" s="5" customFormat="1" ht="26.25" customHeight="1">
-      <c r="A1" s="233" t="s">
+    <row r="1" spans="1:20" s="5" customFormat="1" ht="26.25" customHeight="1">
+      <c r="A1" s="232" t="s">
         <v>2145</v>
       </c>
-      <c r="B1" s="234"/>
-      <c r="C1" s="234"/>
-      <c r="D1" s="234"/>
-      <c r="E1" s="234"/>
-      <c r="F1" s="234"/>
-      <c r="G1" s="234"/>
-      <c r="H1" s="234"/>
-      <c r="I1" s="234"/>
-      <c r="J1" s="234"/>
-      <c r="K1" s="234"/>
-      <c r="L1" s="234"/>
-      <c r="M1" s="235"/>
-    </row>
-    <row r="2" spans="1:19" s="5" customFormat="1" ht="19.5" customHeight="1">
-      <c r="A2" s="225" t="s">
+      <c r="B1" s="233"/>
+      <c r="C1" s="233"/>
+      <c r="D1" s="233"/>
+      <c r="E1" s="233"/>
+      <c r="F1" s="233"/>
+      <c r="G1" s="233"/>
+      <c r="H1" s="233"/>
+      <c r="I1" s="233"/>
+      <c r="J1" s="233"/>
+      <c r="K1" s="233"/>
+      <c r="L1" s="233"/>
+      <c r="M1" s="234"/>
+    </row>
+    <row r="2" spans="1:20" s="5" customFormat="1" ht="19.5" customHeight="1">
+      <c r="A2" s="224" t="s">
         <v>2146</v>
       </c>
-      <c r="B2" s="226"/>
-      <c r="C2" s="226"/>
-      <c r="D2" s="226"/>
-      <c r="E2" s="226"/>
-      <c r="F2" s="226"/>
-      <c r="G2" s="226"/>
-      <c r="H2" s="226"/>
-      <c r="I2" s="226"/>
-      <c r="J2" s="226"/>
-      <c r="K2" s="226"/>
-      <c r="L2" s="226"/>
-      <c r="M2" s="227"/>
-    </row>
-    <row r="3" spans="1:19" s="5" customFormat="1" ht="27" hidden="1" customHeight="1">
-      <c r="A3" s="238" t="s">
+      <c r="B2" s="225"/>
+      <c r="C2" s="225"/>
+      <c r="D2" s="225"/>
+      <c r="E2" s="225"/>
+      <c r="F2" s="225"/>
+      <c r="G2" s="225"/>
+      <c r="H2" s="225"/>
+      <c r="I2" s="225"/>
+      <c r="J2" s="225"/>
+      <c r="K2" s="225"/>
+      <c r="L2" s="225"/>
+      <c r="M2" s="226"/>
+    </row>
+    <row r="3" spans="1:20" s="5" customFormat="1" ht="27" hidden="1" customHeight="1">
+      <c r="A3" s="237" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="219"/>
-      <c r="C3" s="219"/>
-      <c r="D3" s="219"/>
-      <c r="E3" s="219"/>
-      <c r="F3" s="219"/>
-      <c r="G3" s="219"/>
-      <c r="H3" s="219"/>
-      <c r="I3" s="219"/>
-      <c r="J3" s="219"/>
-      <c r="K3" s="219"/>
-      <c r="L3" s="219"/>
-      <c r="M3" s="219"/>
-    </row>
-    <row r="4" spans="1:19" s="5" customFormat="1" ht="41.25" hidden="1" customHeight="1">
-      <c r="A4" s="228" t="s">
+      <c r="B3" s="218"/>
+      <c r="C3" s="218"/>
+      <c r="D3" s="218"/>
+      <c r="E3" s="218"/>
+      <c r="F3" s="218"/>
+      <c r="G3" s="218"/>
+      <c r="H3" s="218"/>
+      <c r="I3" s="218"/>
+      <c r="J3" s="218"/>
+      <c r="K3" s="218"/>
+      <c r="L3" s="218"/>
+      <c r="M3" s="218"/>
+    </row>
+    <row r="4" spans="1:20" s="5" customFormat="1" ht="41.25" hidden="1" customHeight="1">
+      <c r="A4" s="227" t="s">
         <v>2147</v>
       </c>
-      <c r="B4" s="219"/>
-      <c r="C4" s="219"/>
-      <c r="D4" s="219"/>
-      <c r="E4" s="219"/>
-      <c r="F4" s="219"/>
-      <c r="G4" s="219"/>
-      <c r="H4" s="219"/>
-      <c r="I4" s="219"/>
-      <c r="J4" s="219"/>
-      <c r="K4" s="219"/>
-      <c r="L4" s="219"/>
-      <c r="M4" s="219"/>
-    </row>
-    <row r="5" spans="1:19" s="5" customFormat="1" ht="21.75" customHeight="1">
-      <c r="A5" s="232" t="s">
+      <c r="B4" s="218"/>
+      <c r="C4" s="218"/>
+      <c r="D4" s="218"/>
+      <c r="E4" s="218"/>
+      <c r="F4" s="218"/>
+      <c r="G4" s="218"/>
+      <c r="H4" s="218"/>
+      <c r="I4" s="218"/>
+      <c r="J4" s="218"/>
+      <c r="K4" s="218"/>
+      <c r="L4" s="218"/>
+      <c r="M4" s="218"/>
+    </row>
+    <row r="5" spans="1:20" s="5" customFormat="1" ht="21.75" customHeight="1">
+      <c r="A5" s="231" t="s">
         <v>2148</v>
       </c>
-      <c r="B5" s="219"/>
-      <c r="C5" s="219"/>
-      <c r="D5" s="219"/>
-      <c r="E5" s="219"/>
-      <c r="F5" s="219"/>
-      <c r="G5" s="219"/>
-      <c r="H5" s="219"/>
-      <c r="I5" s="219"/>
-      <c r="J5" s="219"/>
-      <c r="K5" s="219"/>
-      <c r="L5" s="219"/>
-      <c r="M5" s="219"/>
-    </row>
-    <row r="6" spans="1:19" s="5" customFormat="1" ht="21.75" customHeight="1">
-      <c r="A6" s="218" t="s">
+      <c r="B5" s="218"/>
+      <c r="C5" s="218"/>
+      <c r="D5" s="218"/>
+      <c r="E5" s="218"/>
+      <c r="F5" s="218"/>
+      <c r="G5" s="218"/>
+      <c r="H5" s="218"/>
+      <c r="I5" s="218"/>
+      <c r="J5" s="218"/>
+      <c r="K5" s="218"/>
+      <c r="L5" s="218"/>
+      <c r="M5" s="218"/>
+    </row>
+    <row r="6" spans="1:20" s="5" customFormat="1" ht="21.75" customHeight="1">
+      <c r="A6" s="217" t="s">
         <v>9</v>
       </c>
-      <c r="B6" s="219"/>
-      <c r="C6" s="219"/>
-      <c r="D6" s="219"/>
-      <c r="E6" s="219"/>
-      <c r="F6" s="219"/>
-      <c r="G6" s="219"/>
-      <c r="H6" s="219"/>
-      <c r="I6" s="219"/>
-      <c r="J6" s="219"/>
-      <c r="K6" s="219"/>
-      <c r="L6" s="219"/>
-      <c r="M6" s="220"/>
-    </row>
-    <row r="7" spans="1:19" s="5" customFormat="1" ht="17.25" customHeight="1">
+      <c r="B6" s="218"/>
+      <c r="C6" s="218"/>
+      <c r="D6" s="218"/>
+      <c r="E6" s="218"/>
+      <c r="F6" s="218"/>
+      <c r="G6" s="218"/>
+      <c r="H6" s="218"/>
+      <c r="I6" s="218"/>
+      <c r="J6" s="218"/>
+      <c r="K6" s="218"/>
+      <c r="L6" s="218"/>
+      <c r="M6" s="219"/>
+    </row>
+    <row r="7" spans="1:20" s="5" customFormat="1" ht="17.25" customHeight="1">
       <c r="A7" s="2" t="s">
         <v>10</v>
       </c>
@@ -37510,8 +37559,11 @@
       <c r="S7" s="5" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="8" spans="1:19" s="175" customFormat="1" ht="15" customHeight="1">
+      <c r="T7" s="5" t="s">
+        <v>3186</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" s="175" customFormat="1" ht="15" customHeight="1">
       <c r="A8" s="168" t="s">
         <v>2150</v>
       </c>
@@ -37538,7 +37590,7 @@
       <c r="L8" s="173"/>
       <c r="M8" s="174"/>
     </row>
-    <row r="9" spans="1:19" s="175" customFormat="1" ht="15" customHeight="1">
+    <row r="9" spans="1:20" s="175" customFormat="1" ht="15" customHeight="1">
       <c r="A9" s="168" t="s">
         <v>2153</v>
       </c>
@@ -37565,7 +37617,7 @@
       <c r="L9" s="173"/>
       <c r="M9" s="174"/>
     </row>
-    <row r="10" spans="1:19" s="175" customFormat="1" ht="15" customHeight="1">
+    <row r="10" spans="1:20" s="175" customFormat="1" ht="15" customHeight="1">
       <c r="A10" s="168" t="s">
         <v>2155</v>
       </c>
@@ -37592,7 +37644,7 @@
       <c r="L10" s="173"/>
       <c r="M10" s="174"/>
     </row>
-    <row r="11" spans="1:19" s="175" customFormat="1" ht="15" customHeight="1">
+    <row r="11" spans="1:20" s="175" customFormat="1" ht="15" customHeight="1">
       <c r="A11" s="168" t="s">
         <v>2158</v>
       </c>
@@ -37617,7 +37669,7 @@
       <c r="L11" s="173"/>
       <c r="M11" s="174"/>
     </row>
-    <row r="12" spans="1:19" s="175" customFormat="1" ht="15" customHeight="1">
+    <row r="12" spans="1:20" s="175" customFormat="1" ht="15" customHeight="1">
       <c r="A12" s="168" t="s">
         <v>2159</v>
       </c>
@@ -37644,7 +37696,7 @@
       <c r="L12" s="173"/>
       <c r="M12" s="174"/>
     </row>
-    <row r="13" spans="1:19" s="175" customFormat="1" ht="15" customHeight="1">
+    <row r="13" spans="1:20" s="175" customFormat="1" ht="15" customHeight="1">
       <c r="A13" s="168" t="s">
         <v>2161</v>
       </c>
@@ -37671,7 +37723,7 @@
       <c r="L13" s="173"/>
       <c r="M13" s="174"/>
     </row>
-    <row r="14" spans="1:19" s="175" customFormat="1" ht="15" customHeight="1">
+    <row r="14" spans="1:20" s="175" customFormat="1" ht="15" customHeight="1">
       <c r="A14" s="168" t="s">
         <v>2163</v>
       </c>
@@ -37697,7 +37749,7 @@
       <c r="L14" s="173"/>
       <c r="M14" s="174"/>
     </row>
-    <row r="15" spans="1:19" s="175" customFormat="1" ht="15" customHeight="1">
+    <row r="15" spans="1:20" s="175" customFormat="1" ht="15" customHeight="1">
       <c r="A15" s="168" t="s">
         <v>2165</v>
       </c>
@@ -37724,7 +37776,7 @@
       <c r="L15" s="173"/>
       <c r="M15" s="174"/>
     </row>
-    <row r="16" spans="1:19" s="175" customFormat="1" ht="15" customHeight="1">
+    <row r="16" spans="1:20" s="175" customFormat="1" ht="15" customHeight="1">
       <c r="A16" s="168" t="s">
         <v>2166</v>
       </c>
@@ -37755,7 +37807,7 @@
       <c r="N16" s="175" t="s">
         <v>2015</v>
       </c>
-      <c r="O16" s="217" t="s">
+      <c r="O16" s="175" t="s">
         <v>2015</v>
       </c>
     </row>
@@ -37898,7 +37950,7 @@
       <c r="N21" s="175" t="s">
         <v>2015</v>
       </c>
-      <c r="O21" s="217" t="s">
+      <c r="O21" s="175" t="s">
         <v>2015</v>
       </c>
       <c r="P21" s="175" t="s">
@@ -37945,7 +37997,7 @@
       <c r="N22" s="175" t="s">
         <v>2015</v>
       </c>
-      <c r="O22" s="217" t="s">
+      <c r="O22" s="175" t="s">
         <v>2015</v>
       </c>
       <c r="P22" s="175" t="s">
@@ -38226,7 +38278,7 @@
       <c r="N32" s="175" t="s">
         <v>2015</v>
       </c>
-      <c r="O32" s="217" t="s">
+      <c r="O32" s="175" t="s">
         <v>2015</v>
       </c>
       <c r="P32" s="175" t="s">
@@ -38460,7 +38512,7 @@
       <c r="N40" s="175" t="s">
         <v>2015</v>
       </c>
-      <c r="O40" s="217" t="s">
+      <c r="O40" s="175" t="s">
         <v>2015</v>
       </c>
     </row>
@@ -38601,7 +38653,7 @@
       <c r="N45" s="175" t="s">
         <v>2015</v>
       </c>
-      <c r="O45" s="217" t="s">
+      <c r="O45" s="175" t="s">
         <v>2015</v>
       </c>
       <c r="P45" s="175" t="s">
@@ -38673,7 +38725,7 @@
       <c r="N47" s="175" t="s">
         <v>2015</v>
       </c>
-      <c r="O47" s="217" t="s">
+      <c r="O47" s="175" t="s">
         <v>2015</v>
       </c>
       <c r="P47" s="175" t="s">
@@ -38774,7 +38826,7 @@
       <c r="N50" s="175" t="s">
         <v>2015</v>
       </c>
-      <c r="O50" s="217" t="s">
+      <c r="O50" s="175" t="s">
         <v>2015</v>
       </c>
     </row>
@@ -38838,7 +38890,7 @@
       <c r="N52" s="175" t="s">
         <v>2015</v>
       </c>
-      <c r="O52" s="217" t="s">
+      <c r="O52" s="175" t="s">
         <v>2015</v>
       </c>
     </row>
@@ -38950,7 +39002,7 @@
       <c r="N56" s="175" t="s">
         <v>2015</v>
       </c>
-      <c r="O56" s="217" t="s">
+      <c r="O56" s="175" t="s">
         <v>2015</v>
       </c>
     </row>
@@ -39007,6 +39059,12 @@
       <c r="K58" s="172"/>
       <c r="L58" s="172"/>
       <c r="M58" s="174"/>
+      <c r="N58" s="175" t="s">
+        <v>3180</v>
+      </c>
+      <c r="O58" s="175" t="s">
+        <v>3180</v>
+      </c>
     </row>
     <row r="59" spans="1:19" s="175" customFormat="1" ht="17.25" customHeight="1">
       <c r="A59" s="168" t="s">
@@ -39059,6 +39117,12 @@
       <c r="K60" s="172"/>
       <c r="L60" s="172"/>
       <c r="M60" s="174"/>
+      <c r="N60" s="175" t="s">
+        <v>3181</v>
+      </c>
+      <c r="O60" s="175" t="s">
+        <v>3181</v>
+      </c>
     </row>
     <row r="61" spans="1:19" s="175" customFormat="1" ht="17.25" customHeight="1">
       <c r="A61" s="168" t="s">
@@ -39172,7 +39236,7 @@
       <c r="N64" s="175" t="s">
         <v>2015</v>
       </c>
-      <c r="O64" s="217" t="s">
+      <c r="O64" s="175" t="s">
         <v>2015</v>
       </c>
       <c r="P64" s="175">
@@ -39188,7 +39252,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="65" spans="1:15" s="175" customFormat="1" ht="17.25" customHeight="1">
+    <row r="65" spans="1:19" s="175" customFormat="1" ht="17.25" customHeight="1">
       <c r="A65" s="168" t="s">
         <v>2261</v>
       </c>
@@ -39215,7 +39279,7 @@
       <c r="L65" s="169"/>
       <c r="M65" s="168"/>
     </row>
-    <row r="66" spans="1:15" s="175" customFormat="1" ht="17.25" customHeight="1">
+    <row r="66" spans="1:19" s="175" customFormat="1" ht="17.25" customHeight="1">
       <c r="A66" s="168" t="s">
         <v>2263</v>
       </c>
@@ -39241,8 +39305,26 @@
       <c r="K66" s="169"/>
       <c r="L66" s="169"/>
       <c r="M66" s="168"/>
-    </row>
-    <row r="67" spans="1:15" s="175" customFormat="1" ht="17.25" customHeight="1">
+      <c r="N66" s="175" t="s">
+        <v>3182</v>
+      </c>
+      <c r="O66" s="175" t="s">
+        <v>3182</v>
+      </c>
+      <c r="P66" s="175" t="s">
+        <v>3183</v>
+      </c>
+      <c r="Q66" s="175">
+        <v>1</v>
+      </c>
+      <c r="R66" s="175" t="s">
+        <v>3184</v>
+      </c>
+      <c r="S66" s="175" t="s">
+        <v>3185</v>
+      </c>
+    </row>
+    <row r="67" spans="1:19" s="175" customFormat="1" ht="17.25" customHeight="1">
       <c r="A67" s="168" t="s">
         <v>2265</v>
       </c>
@@ -39273,11 +39355,11 @@
       <c r="N67" s="175" t="s">
         <v>2015</v>
       </c>
-      <c r="O67" s="217" t="s">
+      <c r="O67" s="175" t="s">
         <v>2015</v>
       </c>
     </row>
-    <row r="68" spans="1:15" s="175" customFormat="1" ht="17.25" customHeight="1">
+    <row r="68" spans="1:19" s="175" customFormat="1" ht="17.25" customHeight="1">
       <c r="A68" s="168" t="s">
         <v>2267</v>
       </c>
@@ -39304,7 +39386,7 @@
       <c r="L68" s="169"/>
       <c r="M68" s="168"/>
     </row>
-    <row r="69" spans="1:15" s="175" customFormat="1" ht="17.25" customHeight="1">
+    <row r="69" spans="1:19" s="175" customFormat="1" ht="17.25" customHeight="1">
       <c r="A69" s="168" t="s">
         <v>2269</v>
       </c>
@@ -39331,7 +39413,7 @@
       <c r="L69" s="169"/>
       <c r="M69" s="168"/>
     </row>
-    <row r="70" spans="1:15" s="175" customFormat="1" ht="17.25" customHeight="1">
+    <row r="70" spans="1:19" s="175" customFormat="1" ht="17.25" customHeight="1">
       <c r="A70" s="168" t="s">
         <v>2271</v>
       </c>
@@ -39357,8 +39439,14 @@
       <c r="K70" s="169"/>
       <c r="L70" s="169"/>
       <c r="M70" s="168"/>
-    </row>
-    <row r="71" spans="1:15" s="175" customFormat="1" ht="17.25" customHeight="1">
+      <c r="N70" s="175" t="s">
+        <v>3179</v>
+      </c>
+      <c r="O70" s="175" t="s">
+        <v>3179</v>
+      </c>
+    </row>
+    <row r="71" spans="1:19" s="175" customFormat="1" ht="17.25" customHeight="1">
       <c r="A71" s="168" t="s">
         <v>2275</v>
       </c>
@@ -39385,7 +39473,7 @@
       <c r="L71" s="169"/>
       <c r="M71" s="168"/>
     </row>
-    <row r="72" spans="1:15" s="175" customFormat="1" ht="17.25" customHeight="1">
+    <row r="72" spans="1:19" s="175" customFormat="1" ht="17.25" customHeight="1">
       <c r="A72" s="168" t="s">
         <v>2277</v>
       </c>
@@ -39412,7 +39500,7 @@
       <c r="L72" s="169"/>
       <c r="M72" s="168"/>
     </row>
-    <row r="73" spans="1:15" s="175" customFormat="1" ht="17.25" customHeight="1">
+    <row r="73" spans="1:19" s="175" customFormat="1" ht="17.25" customHeight="1">
       <c r="A73" s="168" t="s">
         <v>2279</v>
       </c>
@@ -39439,7 +39527,7 @@
       <c r="L73" s="169"/>
       <c r="M73" s="168"/>
     </row>
-    <row r="74" spans="1:15" s="175" customFormat="1" ht="17.25" customHeight="1">
+    <row r="74" spans="1:19" s="175" customFormat="1" ht="17.25" customHeight="1">
       <c r="A74" s="168" t="s">
         <v>2282</v>
       </c>
@@ -39466,7 +39554,7 @@
       <c r="L74" s="169"/>
       <c r="M74" s="168"/>
     </row>
-    <row r="75" spans="1:15" s="175" customFormat="1" ht="17.25" customHeight="1">
+    <row r="75" spans="1:19" s="175" customFormat="1" ht="17.25" customHeight="1">
       <c r="A75" s="168" t="s">
         <v>2284</v>
       </c>
@@ -39493,7 +39581,7 @@
       <c r="L75" s="169"/>
       <c r="M75" s="168"/>
     </row>
-    <row r="76" spans="1:15" s="175" customFormat="1" ht="17.25" customHeight="1">
+    <row r="76" spans="1:19" s="175" customFormat="1" ht="17.25" customHeight="1">
       <c r="A76" s="168" t="s">
         <v>2287</v>
       </c>
@@ -39520,7 +39608,7 @@
       <c r="L76" s="169"/>
       <c r="M76" s="168"/>
     </row>
-    <row r="77" spans="1:15" s="175" customFormat="1" ht="17.25" customHeight="1">
+    <row r="77" spans="1:19" s="175" customFormat="1" ht="17.25" customHeight="1">
       <c r="A77" s="168" t="s">
         <v>2288</v>
       </c>
@@ -39547,7 +39635,7 @@
       <c r="L77" s="169"/>
       <c r="M77" s="168"/>
     </row>
-    <row r="78" spans="1:15" s="175" customFormat="1" ht="17.25" customHeight="1">
+    <row r="78" spans="1:19" s="175" customFormat="1" ht="17.25" customHeight="1">
       <c r="A78" s="168" t="s">
         <v>2290</v>
       </c>
@@ -39574,7 +39662,7 @@
       <c r="L78" s="169"/>
       <c r="M78" s="168"/>
     </row>
-    <row r="79" spans="1:15" s="175" customFormat="1" ht="17.25" customHeight="1">
+    <row r="79" spans="1:19" s="175" customFormat="1" ht="17.25" customHeight="1">
       <c r="A79" s="168" t="s">
         <v>2292</v>
       </c>
@@ -39601,7 +39689,7 @@
       <c r="L79" s="169"/>
       <c r="M79" s="168"/>
     </row>
-    <row r="80" spans="1:15" s="175" customFormat="1" ht="17.25" customHeight="1">
+    <row r="80" spans="1:19" s="175" customFormat="1" ht="17.25" customHeight="1">
       <c r="A80" s="168" t="s">
         <v>2294</v>
       </c>
@@ -39767,7 +39855,7 @@
       <c r="N85" s="175" t="s">
         <v>2015</v>
       </c>
-      <c r="O85" s="217" t="s">
+      <c r="O85" s="175" t="s">
         <v>3152</v>
       </c>
       <c r="Q85" s="175">
@@ -40429,7 +40517,7 @@
       <c r="N109" s="175" t="s">
         <v>3148</v>
       </c>
-      <c r="O109" s="217" t="s">
+      <c r="O109" s="175" t="s">
         <v>3139</v>
       </c>
     </row>
@@ -40759,7 +40847,7 @@
       <c r="N121" s="175" t="s">
         <v>3139</v>
       </c>
-      <c r="O121" s="217" t="s">
+      <c r="O121" s="175" t="s">
         <v>3139</v>
       </c>
     </row>
@@ -41066,7 +41154,7 @@
       <c r="N132" s="175" t="s">
         <v>3150</v>
       </c>
-      <c r="O132" s="217" t="s">
+      <c r="O132" s="175" t="s">
         <v>3139</v>
       </c>
     </row>
@@ -41352,7 +41440,7 @@
       <c r="N142" s="175" t="s">
         <v>3139</v>
       </c>
-      <c r="O142" s="217" t="s">
+      <c r="O142" s="175" t="s">
         <v>3139</v>
       </c>
     </row>
@@ -41441,7 +41529,7 @@
       <c r="N145" s="175" t="s">
         <v>3139</v>
       </c>
-      <c r="O145" s="217" t="s">
+      <c r="O145" s="175" t="s">
         <v>3139</v>
       </c>
     </row>
@@ -46323,7 +46411,7 @@
       <c r="N322" s="175" t="s">
         <v>3169</v>
       </c>
-      <c r="O322" s="217" t="s">
+      <c r="O322" s="175" t="s">
         <v>3169</v>
       </c>
       <c r="P322" s="175" t="s">
@@ -46428,7 +46516,7 @@
       <c r="N325" s="175" t="s">
         <v>3165</v>
       </c>
-      <c r="O325" s="217" t="s">
+      <c r="O325" s="175" t="s">
         <v>3165</v>
       </c>
       <c r="P325" s="175" t="s">
@@ -47039,7 +47127,7 @@
       <c r="N346" s="175" t="s">
         <v>3160</v>
       </c>
-      <c r="O346" s="217" t="s">
+      <c r="O346" s="175" t="s">
         <v>3160</v>
       </c>
       <c r="P346" s="175" t="s">
@@ -47086,7 +47174,7 @@
       <c r="N347" s="175" t="s">
         <v>3157</v>
       </c>
-      <c r="O347" s="217" t="s">
+      <c r="O347" s="175" t="s">
         <v>3157</v>
       </c>
       <c r="P347" s="175" t="s">
@@ -47295,7 +47383,7 @@
       <c r="N354" s="175" t="s">
         <v>3162</v>
       </c>
-      <c r="O354" s="217" t="s">
+      <c r="O354" s="175" t="s">
         <v>3162</v>
       </c>
       <c r="P354" s="175" t="s">
@@ -49862,7 +49950,7 @@
       <c r="N447" s="175" t="s">
         <v>3178</v>
       </c>
-      <c r="O447" s="217" t="s">
+      <c r="O447" s="175" t="s">
         <v>3178</v>
       </c>
     </row>
@@ -50291,7 +50379,7 @@
       <c r="N462" s="175" t="s">
         <v>3153</v>
       </c>
-      <c r="O462" s="217" t="s">
+      <c r="O462" s="175" t="s">
         <v>3153</v>
       </c>
     </row>
@@ -50324,7 +50412,7 @@
       <c r="N463" s="175" t="s">
         <v>3177</v>
       </c>
-      <c r="O463" s="217" t="s">
+      <c r="O463" s="175" t="s">
         <v>3177</v>
       </c>
     </row>
@@ -50523,7 +50611,7 @@
       <c r="N470" s="175" t="s">
         <v>3173</v>
       </c>
-      <c r="O470" s="217" t="s">
+      <c r="O470" s="175" t="s">
         <v>3173</v>
       </c>
       <c r="P470" s="175" t="s">
@@ -50595,7 +50683,7 @@
       <c r="N472" s="175" t="s">
         <v>3154</v>
       </c>
-      <c r="O472" s="217" t="s">
+      <c r="O472" s="175" t="s">
         <v>3154</v>
       </c>
     </row>
@@ -50707,7 +50795,7 @@
       <c r="N476" s="175" t="s">
         <v>3156</v>
       </c>
-      <c r="O476" s="217" t="s">
+      <c r="O476" s="175" t="s">
         <v>3156</v>
       </c>
     </row>
@@ -50769,7 +50857,7 @@
       <c r="N478" s="175" t="s">
         <v>3139</v>
       </c>
-      <c r="O478" s="217" t="s">
+      <c r="O478" s="175" t="s">
         <v>3139</v>
       </c>
     </row>
@@ -50829,11 +50917,11 @@
       <c r="N480" s="175" t="s">
         <v>3155</v>
       </c>
-      <c r="O480" s="217" t="s">
+      <c r="O480" s="175" t="s">
         <v>3155</v>
       </c>
     </row>
-    <row r="481" spans="1:13" s="175" customFormat="1" ht="16.5" customHeight="1">
+    <row r="481" spans="1:20" s="175" customFormat="1" ht="16.5" customHeight="1">
       <c r="A481" s="168" t="s">
         <v>3070</v>
       </c>
@@ -50860,7 +50948,7 @@
       <c r="L481" s="169"/>
       <c r="M481" s="168"/>
     </row>
-    <row r="482" spans="1:13" s="175" customFormat="1" ht="16.5" customHeight="1">
+    <row r="482" spans="1:20" s="175" customFormat="1" ht="16.5" customHeight="1">
       <c r="A482" s="168" t="s">
         <v>3071</v>
       </c>
@@ -50887,7 +50975,7 @@
       <c r="L482" s="169"/>
       <c r="M482" s="168"/>
     </row>
-    <row r="483" spans="1:13" s="175" customFormat="1" ht="16.5" customHeight="1">
+    <row r="483" spans="1:20" s="175" customFormat="1" ht="16.5" customHeight="1">
       <c r="A483" s="168" t="s">
         <v>3073</v>
       </c>
@@ -50912,7 +51000,7 @@
       <c r="L483" s="169"/>
       <c r="M483" s="168"/>
     </row>
-    <row r="484" spans="1:13" s="175" customFormat="1" ht="16.5" customHeight="1">
+    <row r="484" spans="1:20" s="175" customFormat="1" ht="16.5" customHeight="1">
       <c r="A484" s="168" t="s">
         <v>3075</v>
       </c>
@@ -50941,7 +51029,7 @@
       <c r="L484" s="169"/>
       <c r="M484" s="168"/>
     </row>
-    <row r="485" spans="1:13" s="175" customFormat="1" ht="16.5" customHeight="1">
+    <row r="485" spans="1:20" s="175" customFormat="1" ht="16.5" customHeight="1">
       <c r="A485" s="168" t="s">
         <v>3077</v>
       </c>
@@ -50966,7 +51054,7 @@
       <c r="L485" s="169"/>
       <c r="M485" s="168"/>
     </row>
-    <row r="486" spans="1:13" s="175" customFormat="1" ht="16.5" customHeight="1">
+    <row r="486" spans="1:20" s="175" customFormat="1" ht="16.5" customHeight="1">
       <c r="A486" s="168" t="s">
         <v>3079</v>
       </c>
@@ -50993,24 +51081,51 @@
       <c r="L486" s="169"/>
       <c r="M486" s="168"/>
     </row>
-    <row r="487" spans="1:13" s="175" customFormat="1" ht="16.5" customHeight="1">
+    <row r="487" spans="1:20" s="175" customFormat="1" ht="16.5" customHeight="1">
       <c r="A487" s="168" t="s">
         <v>3082</v>
       </c>
-      <c r="B487" s="169"/>
-      <c r="C487" s="168"/>
-      <c r="D487" s="168"/>
+      <c r="B487" s="169" t="s">
+        <v>3190</v>
+      </c>
+      <c r="C487" s="168" t="s">
+        <v>3191</v>
+      </c>
+      <c r="D487" s="168" t="s">
+        <v>3192</v>
+      </c>
       <c r="E487" s="168"/>
-      <c r="F487" s="168"/>
-      <c r="G487" s="168"/>
-      <c r="H487" s="168"/>
+      <c r="F487" s="175" t="s">
+        <v>3193</v>
+      </c>
       <c r="I487" s="168"/>
       <c r="J487" s="192"/>
       <c r="K487" s="169"/>
       <c r="L487" s="169"/>
       <c r="M487" s="168"/>
-    </row>
-    <row r="488" spans="1:13" s="175" customFormat="1" ht="16.5" customHeight="1">
+      <c r="N487" s="175" t="s">
+        <v>3189</v>
+      </c>
+      <c r="O487" s="175" t="s">
+        <v>3139</v>
+      </c>
+      <c r="P487" s="168" t="s">
+        <v>3187</v>
+      </c>
+      <c r="Q487" s="175">
+        <v>1</v>
+      </c>
+      <c r="R487" s="175">
+        <v>11</v>
+      </c>
+      <c r="S487" s="168" t="s">
+        <v>3188</v>
+      </c>
+      <c r="T487" s="168">
+        <v>2291655</v>
+      </c>
+    </row>
+    <row r="488" spans="1:20" s="175" customFormat="1" ht="16.5" customHeight="1">
       <c r="A488" s="168" t="s">
         <v>3083</v>
       </c>
@@ -51027,7 +51142,7 @@
       <c r="L488" s="169"/>
       <c r="M488" s="168"/>
     </row>
-    <row r="489" spans="1:13" s="175" customFormat="1" ht="16.5" customHeight="1">
+    <row r="489" spans="1:20" s="175" customFormat="1" ht="16.5" customHeight="1">
       <c r="A489" s="168" t="s">
         <v>3084</v>
       </c>
@@ -51044,7 +51159,7 @@
       <c r="L489" s="169"/>
       <c r="M489" s="168"/>
     </row>
-    <row r="490" spans="1:13" s="175" customFormat="1" ht="16.5" customHeight="1">
+    <row r="490" spans="1:20" s="175" customFormat="1" ht="16.5" customHeight="1">
       <c r="A490" s="168" t="s">
         <v>3085</v>
       </c>
@@ -51061,7 +51176,7 @@
       <c r="L490" s="169"/>
       <c r="M490" s="168"/>
     </row>
-    <row r="491" spans="1:13" s="175" customFormat="1" ht="16.5" customHeight="1">
+    <row r="491" spans="1:20" s="175" customFormat="1" ht="16.5" customHeight="1">
       <c r="A491" s="168" t="s">
         <v>3086</v>
       </c>
@@ -51078,7 +51193,7 @@
       <c r="L491" s="169"/>
       <c r="M491" s="168"/>
     </row>
-    <row r="492" spans="1:13" s="175" customFormat="1" ht="16.5" customHeight="1">
+    <row r="492" spans="1:20" s="175" customFormat="1" ht="16.5" customHeight="1">
       <c r="A492" s="168" t="s">
         <v>3087</v>
       </c>
@@ -51095,7 +51210,7 @@
       <c r="L492" s="169"/>
       <c r="M492" s="168"/>
     </row>
-    <row r="493" spans="1:13" s="175" customFormat="1" ht="16.5" customHeight="1">
+    <row r="493" spans="1:20" s="175" customFormat="1" ht="16.5" customHeight="1">
       <c r="A493" s="168" t="s">
         <v>3088</v>
       </c>
@@ -51112,7 +51227,7 @@
       <c r="L493" s="169"/>
       <c r="M493" s="168"/>
     </row>
-    <row r="494" spans="1:13" s="175" customFormat="1" ht="16.5" customHeight="1">
+    <row r="494" spans="1:20" s="175" customFormat="1" ht="16.5" customHeight="1">
       <c r="A494" s="168" t="s">
         <v>3089</v>
       </c>
@@ -51129,7 +51244,7 @@
       <c r="L494" s="169"/>
       <c r="M494" s="168"/>
     </row>
-    <row r="495" spans="1:13" s="175" customFormat="1" ht="16.5" customHeight="1">
+    <row r="495" spans="1:20" s="175" customFormat="1" ht="16.5" customHeight="1">
       <c r="A495" s="168" t="s">
         <v>3090</v>
       </c>
@@ -51146,7 +51261,7 @@
       <c r="L495" s="169"/>
       <c r="M495" s="168"/>
     </row>
-    <row r="496" spans="1:13" s="175" customFormat="1" ht="16.5" customHeight="1">
+    <row r="496" spans="1:20" s="175" customFormat="1" ht="16.5" customHeight="1">
       <c r="A496" s="168" t="s">
         <v>3091</v>
       </c>
@@ -51707,7 +51822,7 @@
       <c r="L528" s="169"/>
       <c r="M528" s="168"/>
     </row>
-    <row r="529" spans="1:13" s="175" customFormat="1" ht="16.5" customHeight="1">
+    <row r="529" spans="1:19" s="175" customFormat="1" ht="16.5" customHeight="1">
       <c r="A529" s="168" t="s">
         <v>3124</v>
       </c>
@@ -51724,7 +51839,7 @@
       <c r="L529" s="169"/>
       <c r="M529" s="168"/>
     </row>
-    <row r="530" spans="1:13" s="175" customFormat="1" ht="16.5" customHeight="1">
+    <row r="530" spans="1:19" s="175" customFormat="1" ht="16.5" customHeight="1">
       <c r="A530" s="168" t="s">
         <v>3125</v>
       </c>
@@ -51741,7 +51856,7 @@
       <c r="L530" s="169"/>
       <c r="M530" s="168"/>
     </row>
-    <row r="531" spans="1:13" s="175" customFormat="1" ht="16.5" customHeight="1">
+    <row r="531" spans="1:19" s="175" customFormat="1" ht="16.5" customHeight="1">
       <c r="A531" s="168" t="s">
         <v>3126</v>
       </c>
@@ -51758,7 +51873,7 @@
       <c r="L531" s="169"/>
       <c r="M531" s="168"/>
     </row>
-    <row r="532" spans="1:13" s="175" customFormat="1" ht="16.5" customHeight="1">
+    <row r="532" spans="1:19" s="175" customFormat="1" ht="16.5" customHeight="1">
       <c r="A532" s="168" t="s">
         <v>3127</v>
       </c>
@@ -51775,7 +51890,7 @@
       <c r="L532" s="169"/>
       <c r="M532" s="168"/>
     </row>
-    <row r="533" spans="1:13" s="175" customFormat="1" ht="16.5" customHeight="1">
+    <row r="533" spans="1:19" s="175" customFormat="1" ht="16.5" customHeight="1">
       <c r="A533" s="168" t="s">
         <v>3128</v>
       </c>
@@ -51792,7 +51907,7 @@
       <c r="L533" s="169"/>
       <c r="M533" s="168"/>
     </row>
-    <row r="534" spans="1:13" s="175" customFormat="1" ht="16.5" customHeight="1">
+    <row r="534" spans="1:19" s="175" customFormat="1" ht="16.5" customHeight="1">
       <c r="A534" s="168" t="s">
         <v>3129</v>
       </c>
@@ -51809,7 +51924,7 @@
       <c r="L534" s="169"/>
       <c r="M534" s="168"/>
     </row>
-    <row r="535" spans="1:13" s="175" customFormat="1" ht="16.5" customHeight="1">
+    <row r="535" spans="1:19" s="175" customFormat="1" ht="16.5" customHeight="1">
       <c r="A535" s="168" t="s">
         <v>3130</v>
       </c>
@@ -51826,7 +51941,7 @@
       <c r="L535" s="169"/>
       <c r="M535" s="168"/>
     </row>
-    <row r="536" spans="1:13" s="175" customFormat="1" ht="16.5" customHeight="1">
+    <row r="536" spans="1:19" s="175" customFormat="1" ht="16.5" customHeight="1">
       <c r="A536" s="168" t="s">
         <v>3131</v>
       </c>
@@ -51843,7 +51958,7 @@
       <c r="L536" s="169"/>
       <c r="M536" s="168"/>
     </row>
-    <row r="537" spans="1:13" s="175" customFormat="1" ht="16.5" customHeight="1">
+    <row r="537" spans="1:19" s="175" customFormat="1" ht="16.5" customHeight="1">
       <c r="A537" s="168" t="s">
         <v>3132</v>
       </c>
@@ -51859,6 +51974,286 @@
       <c r="K537" s="169"/>
       <c r="L537" s="169"/>
       <c r="M537" s="168"/>
+    </row>
+    <row r="538" spans="1:19">
+      <c r="N538" s="175"/>
+      <c r="O538" s="175"/>
+      <c r="P538" s="175"/>
+      <c r="Q538" s="175"/>
+      <c r="R538" s="175"/>
+      <c r="S538" s="175"/>
+    </row>
+    <row r="539" spans="1:19">
+      <c r="N539" s="175"/>
+      <c r="O539" s="175"/>
+      <c r="P539" s="175"/>
+      <c r="Q539" s="175"/>
+      <c r="R539" s="175"/>
+      <c r="S539" s="175"/>
+    </row>
+    <row r="540" spans="1:19">
+      <c r="N540" s="175"/>
+      <c r="O540" s="175"/>
+      <c r="P540" s="175"/>
+      <c r="Q540" s="175"/>
+      <c r="R540" s="175"/>
+      <c r="S540" s="175"/>
+    </row>
+    <row r="541" spans="1:19">
+      <c r="N541" s="175"/>
+      <c r="O541" s="175"/>
+      <c r="P541" s="175"/>
+      <c r="Q541" s="175"/>
+      <c r="R541" s="175"/>
+      <c r="S541" s="175"/>
+    </row>
+    <row r="542" spans="1:19">
+      <c r="N542" s="175"/>
+      <c r="O542" s="175"/>
+      <c r="P542" s="175"/>
+      <c r="Q542" s="175"/>
+      <c r="R542" s="175"/>
+      <c r="S542" s="175"/>
+    </row>
+    <row r="543" spans="1:19">
+      <c r="N543" s="175"/>
+      <c r="O543" s="175"/>
+      <c r="P543" s="175"/>
+      <c r="Q543" s="175"/>
+      <c r="R543" s="175"/>
+      <c r="S543" s="175"/>
+    </row>
+    <row r="544" spans="1:19">
+      <c r="N544" s="175"/>
+      <c r="O544" s="175"/>
+      <c r="P544" s="175"/>
+      <c r="Q544" s="175"/>
+      <c r="R544" s="175"/>
+      <c r="S544" s="175"/>
+    </row>
+    <row r="545" spans="14:19">
+      <c r="N545" s="175"/>
+      <c r="O545" s="175"/>
+      <c r="P545" s="175"/>
+      <c r="Q545" s="175"/>
+      <c r="R545" s="175"/>
+      <c r="S545" s="175"/>
+    </row>
+    <row r="546" spans="14:19">
+      <c r="N546" s="175"/>
+      <c r="O546" s="175"/>
+      <c r="P546" s="175"/>
+      <c r="Q546" s="175"/>
+      <c r="R546" s="175"/>
+      <c r="S546" s="175"/>
+    </row>
+    <row r="547" spans="14:19">
+      <c r="N547" s="175"/>
+      <c r="O547" s="175"/>
+      <c r="P547" s="175"/>
+      <c r="Q547" s="175"/>
+      <c r="R547" s="175"/>
+      <c r="S547" s="175"/>
+    </row>
+    <row r="548" spans="14:19">
+      <c r="N548" s="175"/>
+      <c r="O548" s="175"/>
+      <c r="P548" s="175"/>
+      <c r="Q548" s="175"/>
+      <c r="R548" s="175"/>
+      <c r="S548" s="175"/>
+    </row>
+    <row r="549" spans="14:19">
+      <c r="N549" s="175"/>
+      <c r="O549" s="175"/>
+      <c r="P549" s="175"/>
+      <c r="Q549" s="175"/>
+      <c r="R549" s="175"/>
+      <c r="S549" s="175"/>
+    </row>
+    <row r="550" spans="14:19">
+      <c r="N550" s="175"/>
+      <c r="O550" s="175"/>
+      <c r="P550" s="175"/>
+      <c r="Q550" s="175"/>
+      <c r="R550" s="175"/>
+      <c r="S550" s="175"/>
+    </row>
+    <row r="551" spans="14:19">
+      <c r="N551" s="175"/>
+      <c r="O551" s="175"/>
+      <c r="P551" s="175"/>
+      <c r="Q551" s="175"/>
+      <c r="R551" s="175"/>
+      <c r="S551" s="175"/>
+    </row>
+    <row r="552" spans="14:19">
+      <c r="N552" s="175"/>
+      <c r="O552" s="175"/>
+      <c r="P552" s="175"/>
+      <c r="Q552" s="175"/>
+      <c r="R552" s="175"/>
+      <c r="S552" s="175"/>
+    </row>
+    <row r="553" spans="14:19">
+      <c r="N553" s="175"/>
+      <c r="O553" s="175"/>
+      <c r="P553" s="175"/>
+      <c r="Q553" s="175"/>
+      <c r="R553" s="175"/>
+      <c r="S553" s="175"/>
+    </row>
+    <row r="554" spans="14:19">
+      <c r="N554" s="175"/>
+      <c r="O554" s="175"/>
+      <c r="P554" s="175"/>
+      <c r="Q554" s="175"/>
+      <c r="R554" s="175"/>
+      <c r="S554" s="175"/>
+    </row>
+    <row r="555" spans="14:19">
+      <c r="N555" s="175"/>
+      <c r="O555" s="175"/>
+      <c r="P555" s="175"/>
+      <c r="Q555" s="175"/>
+      <c r="R555" s="175"/>
+      <c r="S555" s="175"/>
+    </row>
+    <row r="556" spans="14:19">
+      <c r="N556" s="175"/>
+      <c r="O556" s="175"/>
+      <c r="P556" s="175"/>
+      <c r="Q556" s="175"/>
+      <c r="R556" s="175"/>
+      <c r="S556" s="175"/>
+    </row>
+    <row r="557" spans="14:19">
+      <c r="N557" s="175"/>
+      <c r="O557" s="175"/>
+      <c r="P557" s="175"/>
+      <c r="Q557" s="175"/>
+      <c r="R557" s="175"/>
+      <c r="S557" s="175"/>
+    </row>
+    <row r="558" spans="14:19">
+      <c r="N558" s="175"/>
+      <c r="O558" s="175"/>
+      <c r="P558" s="175"/>
+      <c r="Q558" s="175"/>
+      <c r="R558" s="175"/>
+      <c r="S558" s="175"/>
+    </row>
+    <row r="559" spans="14:19">
+      <c r="N559" s="175"/>
+      <c r="O559" s="175"/>
+      <c r="P559" s="175"/>
+      <c r="Q559" s="175"/>
+      <c r="R559" s="175"/>
+      <c r="S559" s="175"/>
+    </row>
+    <row r="560" spans="14:19">
+      <c r="N560" s="175"/>
+      <c r="O560" s="175"/>
+      <c r="P560" s="175"/>
+      <c r="Q560" s="175"/>
+      <c r="R560" s="175"/>
+      <c r="S560" s="175"/>
+    </row>
+    <row r="561" spans="14:19">
+      <c r="N561" s="175"/>
+      <c r="O561" s="175"/>
+      <c r="P561" s="175"/>
+      <c r="Q561" s="175"/>
+      <c r="R561" s="175"/>
+      <c r="S561" s="175"/>
+    </row>
+    <row r="562" spans="14:19">
+      <c r="N562" s="175"/>
+      <c r="O562" s="175"/>
+      <c r="P562" s="175"/>
+      <c r="Q562" s="175"/>
+      <c r="R562" s="175"/>
+      <c r="S562" s="175"/>
+    </row>
+    <row r="563" spans="14:19">
+      <c r="N563" s="175"/>
+      <c r="O563" s="175"/>
+      <c r="P563" s="175"/>
+      <c r="Q563" s="175"/>
+      <c r="R563" s="175"/>
+      <c r="S563" s="175"/>
+    </row>
+    <row r="564" spans="14:19">
+      <c r="N564" s="175"/>
+      <c r="O564" s="175"/>
+      <c r="P564" s="175"/>
+      <c r="Q564" s="175"/>
+      <c r="R564" s="175"/>
+      <c r="S564" s="175"/>
+    </row>
+    <row r="565" spans="14:19">
+      <c r="N565" s="175"/>
+      <c r="O565" s="175"/>
+      <c r="P565" s="175"/>
+      <c r="Q565" s="175"/>
+      <c r="R565" s="175"/>
+      <c r="S565" s="175"/>
+    </row>
+    <row r="566" spans="14:19">
+      <c r="N566" s="175"/>
+      <c r="O566" s="175"/>
+      <c r="P566" s="175"/>
+      <c r="Q566" s="175"/>
+      <c r="R566" s="175"/>
+      <c r="S566" s="175"/>
+    </row>
+    <row r="567" spans="14:19">
+      <c r="N567" s="175"/>
+      <c r="O567" s="175"/>
+      <c r="P567" s="175"/>
+      <c r="Q567" s="175"/>
+      <c r="R567" s="175"/>
+      <c r="S567" s="175"/>
+    </row>
+    <row r="568" spans="14:19">
+      <c r="N568" s="175"/>
+      <c r="O568" s="175"/>
+      <c r="P568" s="175"/>
+      <c r="Q568" s="175"/>
+      <c r="R568" s="175"/>
+      <c r="S568" s="175"/>
+    </row>
+    <row r="569" spans="14:19">
+      <c r="N569" s="175"/>
+      <c r="O569" s="175"/>
+      <c r="P569" s="175"/>
+      <c r="Q569" s="175"/>
+      <c r="R569" s="175"/>
+      <c r="S569" s="175"/>
+    </row>
+    <row r="570" spans="14:19">
+      <c r="N570" s="175"/>
+      <c r="O570" s="175"/>
+      <c r="P570" s="175"/>
+      <c r="Q570" s="175"/>
+      <c r="R570" s="175"/>
+      <c r="S570" s="175"/>
+    </row>
+    <row r="571" spans="14:19">
+      <c r="N571" s="175"/>
+      <c r="O571" s="175"/>
+      <c r="P571" s="175"/>
+      <c r="Q571" s="175"/>
+      <c r="R571" s="175"/>
+      <c r="S571" s="175"/>
+    </row>
+    <row r="572" spans="14:19">
+      <c r="N572" s="175"/>
+      <c r="O572" s="175"/>
+      <c r="P572" s="175"/>
+      <c r="Q572" s="175"/>
+      <c r="R572" s="175"/>
+      <c r="S572" s="175"/>
     </row>
     <row r="1044938" spans="2:3">
       <c r="C1044938" s="6"/>
